--- a/data/outputs/latest_scorecard.xlsx
+++ b/data/outputs/latest_scorecard.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="90">
   <si>
     <t>country</t>
   </si>
@@ -76,6 +76,9 @@
     <t>end_date</t>
   </si>
   <si>
+    <t>Northern Mariana Is.</t>
+  </si>
+  <si>
     <t>Japan</t>
   </si>
   <si>
@@ -88,16 +91,25 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Myanmar, Thailand</t>
+  </si>
+  <si>
     <t>Laos</t>
+  </si>
+  <si>
+    <t>Myanmar</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bangladesh</t>
   </si>
   <si>
     <t>Venezuela</t>
   </si>
   <si>
-    <t>Myanmar</t>
-  </si>
-  <si>
-    <t>Myanmar, Thailand</t>
+    <t>Bangladesh, Myanmar</t>
   </si>
   <si>
     <t>China</t>
@@ -124,13 +136,7 @@
     <t>Tonga</t>
   </si>
   <si>
-    <t>Philippines</t>
-  </si>
-  <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
-    <t>India</t>
+    <t>MNP</t>
   </si>
   <si>
     <t>JPN</t>
@@ -145,13 +151,19 @@
     <t>THA</t>
   </si>
   <si>
+    <t>MMR</t>
+  </si>
+  <si>
     <t>LAO</t>
   </si>
   <si>
-    <t>VEN</t>
+    <t>IND</t>
   </si>
   <si>
-    <t>MMR</t>
+    <t>BGD</t>
+  </si>
+  <si>
+    <t>VEN</t>
   </si>
   <si>
     <t>CHN</t>
@@ -167,15 +179,6 @@
   </si>
   <si>
     <t>TON</t>
-  </si>
-  <si>
-    <t>PHL</t>
-  </si>
-  <si>
-    <t>PAK</t>
-  </si>
-  <si>
-    <t>IND</t>
   </si>
   <si>
     <t>EQ</t>
@@ -202,6 +205,9 @@
     <t>Prepare response resources</t>
   </si>
   <si>
+    <t>2026-03-29T15:06:26</t>
+  </si>
+  <si>
     <t>2026-03-29T07:07:55</t>
   </si>
   <si>
@@ -211,13 +217,13 @@
     <t>2026-03-29T03:01:58</t>
   </si>
   <si>
-    <t>2026-03-23T00:00:00</t>
-  </si>
-  <si>
     <t>2026-03-25T00:00:00</t>
   </si>
   <si>
     <t>2026-03-24T00:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-23T00:00:00</t>
   </si>
   <si>
     <t>2026-03-22T00:00:00</t>
@@ -232,10 +238,13 @@
     <t>2026-03-19T00:00:00</t>
   </si>
   <si>
-    <t>2026-03-26T00:00:00</t>
+    <t>2026-03-18T00:00:00</t>
   </si>
   <si>
-    <t>2026-03-18T00:00:00</t>
+    <t>2026-03-27T00:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-26T00:00:00</t>
   </si>
   <si>
     <t>2026-03-16T00:00:00</t>
@@ -274,24 +283,6 @@
     <t>2026-03-28T07:35:41</t>
   </si>
   <si>
-    <t>2026-03-28T06:29:14</t>
-  </si>
-  <si>
-    <t>2026-03-28T04:27:07</t>
-  </si>
-  <si>
-    <t>2026-03-28T03:33:57</t>
-  </si>
-  <si>
-    <t>2026-03-28T01:20:01</t>
-  </si>
-  <si>
-    <t>2026-03-27T00:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-28T00:00:00</t>
-  </si>
-  <si>
     <t>2026-03-29T00:00:00</t>
   </si>
 </sst>
@@ -299,8 +290,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -316,7 +315,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -324,12 +323,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -628,64 +645,64 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -694,22 +711,22 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>242.1919191919192</v>
+        <v>2.5</v>
       </c>
       <c r="I2">
-        <v>53860.28571428572</v>
+        <v>286.6666666666667</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -718,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>21.72</v>
+        <v>0.91</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -727,22 +744,22 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>28.69</v>
+        <v>20.36</v>
       </c>
       <c r="P2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -750,22 +767,22 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="H3">
-        <v>44.94444444444444</v>
+        <v>242.1919191919192</v>
       </c>
       <c r="I3">
-        <v>92135.45454545454</v>
+        <v>53860.28571428572</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -774,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>21.72</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -783,22 +800,22 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>23.2</v>
+        <v>28.69</v>
       </c>
       <c r="P3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -806,22 +823,22 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4">
         <v>41</v>
       </c>
-      <c r="C4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4">
-        <v>48</v>
-      </c>
       <c r="H4">
-        <v>417.030303030303</v>
+        <v>44.94444444444444</v>
       </c>
       <c r="I4">
-        <v>5480.307692307692</v>
+        <v>92135.45454545454</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -830,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>12.27</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -839,22 +856,22 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>24.91</v>
+        <v>23.2</v>
       </c>
       <c r="P4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -862,22 +879,22 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="H5">
-        <v>189.2295081967213</v>
+        <v>417.030303030303</v>
       </c>
       <c r="I5">
-        <v>1235122.38028169</v>
+        <v>5480.307692307692</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -886,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>19.9</v>
+        <v>12.27</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -895,22 +912,22 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>27.96</v>
+        <v>24.91</v>
       </c>
       <c r="P5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T5" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -918,22 +935,22 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H6">
-        <v>17.88888888888889</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I6">
-        <v>204634.5909090909</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -942,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>5.65</v>
+        <v>19.9</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -951,45 +968,45 @@
         <v>0</v>
       </c>
       <c r="O6">
-        <v>22.26</v>
+        <v>27.96</v>
       </c>
       <c r="P6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="H7">
-        <v>22.14285714285714</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I7">
-        <v>77954.60000000001</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -998,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>5.79</v>
+        <v>19.9</v>
       </c>
       <c r="M7">
         <v>1</v>
@@ -1007,36 +1024,36 @@
         <v>0</v>
       </c>
       <c r="O7">
-        <v>22.32</v>
+        <v>27.96</v>
       </c>
       <c r="P7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
         <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>49</v>
@@ -1066,33 +1083,33 @@
         <v>35.81</v>
       </c>
       <c r="P8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>79</v>
@@ -1122,42 +1139,42 @@
         <v>27.96</v>
       </c>
       <c r="P9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="T9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="H10">
-        <v>189.2295081967213</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I10">
-        <v>1235122.38028169</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1166,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>19.9</v>
+        <v>5.65</v>
       </c>
       <c r="M10">
         <v>1</v>
@@ -1175,22 +1192,22 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>27.96</v>
+        <v>22.26</v>
       </c>
       <c r="P10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S10" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="T10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1198,22 +1215,22 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H11">
-        <v>3366.372093023256</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I11">
-        <v>242888.6744186046</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1222,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>39.53</v>
+        <v>5.65</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -1231,45 +1248,45 @@
         <v>0</v>
       </c>
       <c r="O11">
-        <v>35.81</v>
+        <v>22.26</v>
       </c>
       <c r="P11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S11" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="T11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="H12">
-        <v>189.2295081967213</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I12">
-        <v>1235122.38028169</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1278,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>19.9</v>
+        <v>5.65</v>
       </c>
       <c r="M12">
         <v>1</v>
@@ -1287,36 +1304,36 @@
         <v>0</v>
       </c>
       <c r="O12">
-        <v>27.96</v>
+        <v>22.26</v>
       </c>
       <c r="P12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="T12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G13">
         <v>49</v>
@@ -1346,42 +1363,42 @@
         <v>35.81</v>
       </c>
       <c r="P13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="T13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="H14">
-        <v>189.2295081967213</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I14">
-        <v>1235122.38028169</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1390,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>19.9</v>
+        <v>39.53</v>
       </c>
       <c r="M14">
         <v>1</v>
@@ -1399,45 +1416,45 @@
         <v>0</v>
       </c>
       <c r="O14">
-        <v>27.96</v>
+        <v>35.81</v>
       </c>
       <c r="P14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="T14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="H15">
-        <v>189.2295081967213</v>
+        <v>524.5260115606936</v>
       </c>
       <c r="I15">
-        <v>1235122.38028169</v>
+        <v>8888767.798449613</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1446,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>19.9</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="M15">
         <v>1</v>
@@ -1455,45 +1472,45 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>27.96</v>
+        <v>46.74</v>
       </c>
       <c r="P15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="H16">
-        <v>189.2295081967213</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I16">
-        <v>1235122.38028169</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1502,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>19.9</v>
+        <v>39.53</v>
       </c>
       <c r="M16">
         <v>1</v>
@@ -1511,45 +1528,45 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>27.96</v>
+        <v>35.81</v>
       </c>
       <c r="P16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="T16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="H17">
-        <v>189.2295081967213</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I17">
-        <v>1235122.38028169</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1558,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>19.9</v>
+        <v>39.53</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -1567,45 +1584,45 @@
         <v>0</v>
       </c>
       <c r="O17">
-        <v>27.96</v>
+        <v>35.81</v>
       </c>
       <c r="P17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S17" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="T17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G18">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="H18">
-        <v>189.2295081967213</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I18">
-        <v>1235122.38028169</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1614,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>19.9</v>
+        <v>5.65</v>
       </c>
       <c r="M18">
         <v>1</v>
@@ -1623,22 +1640,22 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>27.96</v>
+        <v>22.26</v>
       </c>
       <c r="P18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S18" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="T18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1649,10 +1666,10 @@
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19">
         <v>49</v>
@@ -1682,33 +1699,33 @@
         <v>35.81</v>
       </c>
       <c r="P19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S19" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="T19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20">
         <v>79</v>
@@ -1738,42 +1755,42 @@
         <v>27.96</v>
       </c>
       <c r="P20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S20" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="T20" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:20">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="H21">
-        <v>17.88888888888889</v>
+        <v>120.7628865979381</v>
       </c>
       <c r="I21">
-        <v>204634.5909090909</v>
+        <v>1930943.574468085</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1782,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>5.65</v>
+        <v>26.44</v>
       </c>
       <c r="M21">
         <v>1</v>
@@ -1791,45 +1808,45 @@
         <v>0</v>
       </c>
       <c r="O21">
-        <v>22.26</v>
+        <v>30.58</v>
       </c>
       <c r="P21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S21" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="T21" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:20">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G22">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H22">
-        <v>17.88888888888889</v>
+        <v>22.14285714285714</v>
       </c>
       <c r="I22">
-        <v>204634.5909090909</v>
+        <v>77954.60000000001</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1838,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>5.65</v>
+        <v>5.79</v>
       </c>
       <c r="M22">
         <v>1</v>
@@ -1847,45 +1864,45 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>22.26</v>
+        <v>22.32</v>
       </c>
       <c r="P22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:20">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G23">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H23">
-        <v>17.88888888888889</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I23">
-        <v>204634.5909090909</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1894,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>5.65</v>
+        <v>39.53</v>
       </c>
       <c r="M23">
         <v>1</v>
@@ -1903,45 +1920,45 @@
         <v>0</v>
       </c>
       <c r="O23">
-        <v>22.26</v>
+        <v>35.81</v>
       </c>
       <c r="P23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S23" t="s">
         <v>68</v>
       </c>
       <c r="T23" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:20">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G24">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H24">
-        <v>3366.372093023256</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I24">
-        <v>242888.6744186046</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1950,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>39.53</v>
+        <v>19.9</v>
       </c>
       <c r="M24">
         <v>1</v>
@@ -1959,45 +1976,45 @@
         <v>0</v>
       </c>
       <c r="O24">
-        <v>35.81</v>
+        <v>27.96</v>
       </c>
       <c r="P24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S24" t="s">
         <v>69</v>
       </c>
       <c r="T24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:20">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G25">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H25">
-        <v>3366.372093023256</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I25">
-        <v>242888.6744186046</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -2006,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>39.53</v>
+        <v>19.9</v>
       </c>
       <c r="M25">
         <v>1</v>
@@ -2015,36 +2032,36 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <v>35.81</v>
+        <v>27.96</v>
       </c>
       <c r="P25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="T25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:20">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
         <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G26">
         <v>49</v>
@@ -2074,42 +2091,42 @@
         <v>35.81</v>
       </c>
       <c r="P26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:20">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G27">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H27">
-        <v>3366.372093023256</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I27">
-        <v>242888.6744186046</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -2118,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>39.53</v>
+        <v>19.9</v>
       </c>
       <c r="M27">
         <v>1</v>
@@ -2127,45 +2144,45 @@
         <v>0</v>
       </c>
       <c r="O27">
-        <v>35.81</v>
+        <v>27.96</v>
       </c>
       <c r="P27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T27" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:20">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G28">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="H28">
-        <v>189.2295081967213</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I28">
-        <v>1235122.38028169</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -2174,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>19.9</v>
+        <v>39.53</v>
       </c>
       <c r="M28">
         <v>1</v>
@@ -2183,45 +2200,45 @@
         <v>0</v>
       </c>
       <c r="O28">
-        <v>27.96</v>
+        <v>35.81</v>
       </c>
       <c r="P28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S28" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="T28" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:20">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G29">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H29">
-        <v>3366.372093023256</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I29">
-        <v>242888.6744186046</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -2230,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>39.53</v>
+        <v>19.9</v>
       </c>
       <c r="M29">
         <v>1</v>
@@ -2239,36 +2256,36 @@
         <v>0</v>
       </c>
       <c r="O29">
-        <v>35.81</v>
+        <v>27.96</v>
       </c>
       <c r="P29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="T29" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:20">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G30">
         <v>79</v>
@@ -2298,42 +2315,42 @@
         <v>27.96</v>
       </c>
       <c r="P30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="T30" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:20">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G31">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H31">
-        <v>3366.372093023256</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I31">
-        <v>242888.6744186046</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -2342,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>39.53</v>
+        <v>19.9</v>
       </c>
       <c r="M31">
         <v>1</v>
@@ -2351,36 +2368,36 @@
         <v>0</v>
       </c>
       <c r="O31">
-        <v>35.81</v>
+        <v>27.96</v>
       </c>
       <c r="P31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S31" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="T31" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:20">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
         <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G32">
         <v>49</v>
@@ -2410,33 +2427,33 @@
         <v>35.81</v>
       </c>
       <c r="P32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S32" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T32" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:20">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
         <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G33">
         <v>49</v>
@@ -2466,19 +2483,19 @@
         <v>35.81</v>
       </c>
       <c r="P33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S33" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="T33" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -2486,22 +2503,22 @@
         <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G34">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H34">
-        <v>17.88888888888889</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I34">
-        <v>204634.5909090909</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -2510,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>5.65</v>
+        <v>19.9</v>
       </c>
       <c r="M34">
         <v>1</v>
@@ -2519,36 +2536,36 @@
         <v>0</v>
       </c>
       <c r="O34">
-        <v>22.26</v>
+        <v>27.96</v>
       </c>
       <c r="P34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S34" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="T34" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
         <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G35">
         <v>49</v>
@@ -2578,42 +2595,42 @@
         <v>35.81</v>
       </c>
       <c r="P35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="T35" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G36">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H36">
-        <v>3366.372093023256</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I36">
-        <v>242888.6744186046</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -2622,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>39.53</v>
+        <v>19.9</v>
       </c>
       <c r="M36">
         <v>1</v>
@@ -2631,45 +2648,45 @@
         <v>0</v>
       </c>
       <c r="O36">
-        <v>35.81</v>
+        <v>27.96</v>
       </c>
       <c r="P36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S36" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="T36" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G37">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="H37">
-        <v>189.2295081967213</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I37">
-        <v>1235122.38028169</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -2678,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>19.9</v>
+        <v>39.53</v>
       </c>
       <c r="M37">
         <v>1</v>
@@ -2687,45 +2704,45 @@
         <v>0</v>
       </c>
       <c r="O37">
-        <v>27.96</v>
+        <v>35.81</v>
       </c>
       <c r="P37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S37" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="T37" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G38">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="H38">
-        <v>3366.372093023256</v>
+        <v>524.5260115606936</v>
       </c>
       <c r="I38">
-        <v>242888.6744186046</v>
+        <v>8888767.798449613</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2734,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>39.53</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="M38">
         <v>1</v>
@@ -2743,45 +2760,45 @@
         <v>0</v>
       </c>
       <c r="O38">
-        <v>35.81</v>
+        <v>46.74</v>
       </c>
       <c r="P38" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R38" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S38" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T38" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:20">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G39">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="H39">
-        <v>589.8571428571429</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I39">
-        <v>8597932.334951457</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2790,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>74.28</v>
+        <v>19.9</v>
       </c>
       <c r="M39">
         <v>1</v>
@@ -2799,13 +2816,13 @@
         <v>0</v>
       </c>
       <c r="O39">
-        <v>49.71</v>
+        <v>27.96</v>
       </c>
       <c r="P39" t="s">
         <v>58</v>
       </c>
       <c r="Q39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R39" t="s">
         <v>61</v>
@@ -2814,30 +2831,30 @@
         <v>69</v>
       </c>
       <c r="T39" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G40">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="H40">
-        <v>189.2295081967213</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I40">
-        <v>1235122.38028169</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -2846,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>19.9</v>
+        <v>5.65</v>
       </c>
       <c r="M40">
         <v>1</v>
@@ -2855,45 +2872,45 @@
         <v>0</v>
       </c>
       <c r="O40">
-        <v>27.96</v>
+        <v>22.26</v>
       </c>
       <c r="P40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S40" t="s">
         <v>69</v>
       </c>
       <c r="T40" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:20">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G41">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="H41">
-        <v>3366.372093023256</v>
+        <v>120.7628865979381</v>
       </c>
       <c r="I41">
-        <v>242888.6744186046</v>
+        <v>1930943.574468085</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2902,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>39.53</v>
+        <v>26.44</v>
       </c>
       <c r="M41">
         <v>1</v>
@@ -2911,22 +2928,22 @@
         <v>0</v>
       </c>
       <c r="O41">
-        <v>35.81</v>
+        <v>30.58</v>
       </c>
       <c r="P41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S41" t="s">
         <v>69</v>
       </c>
       <c r="T41" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -2934,22 +2951,22 @@
         <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G42">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H42">
-        <v>3366.372093023256</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I42">
-        <v>242888.6744186046</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -2958,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>39.53</v>
+        <v>5.65</v>
       </c>
       <c r="M42">
         <v>1</v>
@@ -2967,36 +2984,36 @@
         <v>0</v>
       </c>
       <c r="O42">
-        <v>35.81</v>
+        <v>22.26</v>
       </c>
       <c r="P42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T42" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:20">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
         <v>45</v>
       </c>
       <c r="C43" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G43">
         <v>49</v>
@@ -3026,42 +3043,42 @@
         <v>35.81</v>
       </c>
       <c r="P43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T43" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:20">
       <c r="A44" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D44" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G44">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H44">
-        <v>17.88888888888889</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I44">
-        <v>204634.5909090909</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3070,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>5.65</v>
+        <v>39.53</v>
       </c>
       <c r="M44">
         <v>1</v>
@@ -3079,45 +3096,45 @@
         <v>0</v>
       </c>
       <c r="O44">
-        <v>22.26</v>
+        <v>35.81</v>
       </c>
       <c r="P44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T44" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G45">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H45">
-        <v>3366.372093023256</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I45">
-        <v>242888.6744186046</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3126,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>39.53</v>
+        <v>19.9</v>
       </c>
       <c r="M45">
         <v>1</v>
@@ -3135,45 +3152,45 @@
         <v>0</v>
       </c>
       <c r="O45">
-        <v>35.81</v>
+        <v>27.96</v>
       </c>
       <c r="P45" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R45" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S45" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="T45" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:20">
       <c r="A46" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G46">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="H46">
-        <v>189.2295081967213</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I46">
-        <v>1235122.38028169</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3182,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>19.9</v>
+        <v>39.53</v>
       </c>
       <c r="M46">
         <v>1</v>
@@ -3191,36 +3208,36 @@
         <v>0</v>
       </c>
       <c r="O46">
-        <v>27.96</v>
+        <v>35.81</v>
       </c>
       <c r="P46" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R46" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S46" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="T46" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G47">
         <v>225</v>
@@ -3250,42 +3267,42 @@
         <v>49.71</v>
       </c>
       <c r="P47" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q47" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S47" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="T47" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:20">
       <c r="A48" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G48">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H48">
-        <v>17.88888888888889</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I48">
-        <v>204634.5909090909</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3294,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>5.65</v>
+        <v>39.53</v>
       </c>
       <c r="M48">
         <v>1</v>
@@ -3303,45 +3320,45 @@
         <v>0</v>
       </c>
       <c r="O48">
-        <v>22.26</v>
+        <v>35.81</v>
       </c>
       <c r="P48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R48" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S48" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="T48" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:20">
       <c r="A49" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G49">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H49">
-        <v>17.88888888888889</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I49">
-        <v>204634.5909090909</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3350,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>5.65</v>
+        <v>39.53</v>
       </c>
       <c r="M49">
         <v>1</v>
@@ -3359,36 +3376,36 @@
         <v>0</v>
       </c>
       <c r="O49">
-        <v>22.26</v>
+        <v>35.81</v>
       </c>
       <c r="P49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q49" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S49" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="T49" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:20">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
         <v>45</v>
       </c>
       <c r="C50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G50">
         <v>49</v>
@@ -3418,42 +3435,42 @@
         <v>35.81</v>
       </c>
       <c r="P50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S50" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="T50" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:20">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G51">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H51">
-        <v>3366.372093023256</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I51">
-        <v>242888.6744186046</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3462,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>39.53</v>
+        <v>19.9</v>
       </c>
       <c r="M51">
         <v>1</v>
@@ -3471,36 +3488,36 @@
         <v>0</v>
       </c>
       <c r="O51">
-        <v>35.81</v>
+        <v>27.96</v>
       </c>
       <c r="P51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T51" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:20">
       <c r="A52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
         <v>45</v>
       </c>
       <c r="C52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G52">
         <v>49</v>
@@ -3530,42 +3547,42 @@
         <v>35.81</v>
       </c>
       <c r="P52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R52" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S52" t="s">
         <v>71</v>
       </c>
       <c r="T52" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:20">
       <c r="A53" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G53">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="H53">
-        <v>3366.372093023256</v>
+        <v>589.8571428571429</v>
       </c>
       <c r="I53">
-        <v>242888.6744186046</v>
+        <v>8597932.334951457</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -3574,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>39.53</v>
+        <v>74.28</v>
       </c>
       <c r="M53">
         <v>1</v>
@@ -3583,22 +3600,22 @@
         <v>0</v>
       </c>
       <c r="O53">
-        <v>35.81</v>
+        <v>49.71</v>
       </c>
       <c r="P53" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R53" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T53" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -3606,22 +3623,22 @@
         <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G54">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H54">
-        <v>3366.372093023256</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I54">
-        <v>242888.6744186046</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3630,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>39.53</v>
+        <v>5.65</v>
       </c>
       <c r="M54">
         <v>1</v>
@@ -3639,22 +3656,22 @@
         <v>0</v>
       </c>
       <c r="O54">
-        <v>35.81</v>
+        <v>22.26</v>
       </c>
       <c r="P54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T54" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:20">
@@ -3662,22 +3679,22 @@
         <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C55" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G55">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H55">
-        <v>3366.372093023256</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I55">
-        <v>242888.6744186046</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3686,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>39.53</v>
+        <v>5.65</v>
       </c>
       <c r="M55">
         <v>1</v>
@@ -3695,36 +3712,36 @@
         <v>0</v>
       </c>
       <c r="O55">
-        <v>35.81</v>
+        <v>22.26</v>
       </c>
       <c r="P55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="T55" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:20">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
         <v>45</v>
       </c>
       <c r="C56" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G56">
         <v>49</v>
@@ -3754,33 +3771,33 @@
         <v>35.81</v>
       </c>
       <c r="P56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R56" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T56" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
         <v>45</v>
       </c>
       <c r="C57" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D57" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G57">
         <v>49</v>
@@ -3810,33 +3827,33 @@
         <v>35.81</v>
       </c>
       <c r="P57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q57" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S57" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="T57" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:20">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
         <v>45</v>
       </c>
       <c r="C58" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D58" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G58">
         <v>49</v>
@@ -3866,42 +3883,42 @@
         <v>35.81</v>
       </c>
       <c r="P58" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R58" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S58" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="T58" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:20">
       <c r="A59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C59" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G59">
-        <v>225</v>
+        <v>49</v>
       </c>
       <c r="H59">
-        <v>589.8571428571429</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I59">
-        <v>8597932.334951457</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -3910,7 +3927,7 @@
         <v>0</v>
       </c>
       <c r="L59">
-        <v>74.28</v>
+        <v>39.53</v>
       </c>
       <c r="M59">
         <v>1</v>
@@ -3919,45 +3936,45 @@
         <v>0</v>
       </c>
       <c r="O59">
-        <v>49.71</v>
+        <v>35.81</v>
       </c>
       <c r="P59" t="s">
         <v>58</v>
       </c>
       <c r="Q59" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R59" t="s">
         <v>61</v>
       </c>
       <c r="S59" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="T59" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C60" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D60" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G60">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H60">
-        <v>12.4</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I60">
-        <v>19377.6</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -3966,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>3.91</v>
+        <v>39.53</v>
       </c>
       <c r="M60">
         <v>1</v>
@@ -3975,36 +3992,36 @@
         <v>0</v>
       </c>
       <c r="O60">
-        <v>21.56</v>
+        <v>35.81</v>
       </c>
       <c r="P60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R60" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S60" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="T60" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B61" t="s">
         <v>45</v>
       </c>
       <c r="C61" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D61" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G61">
         <v>49</v>
@@ -4034,42 +4051,42 @@
         <v>35.81</v>
       </c>
       <c r="P61" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S61" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="T61" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C62" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D62" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G62">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H62">
-        <v>17.88888888888889</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I62">
-        <v>204634.5909090909</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -4078,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>5.65</v>
+        <v>39.53</v>
       </c>
       <c r="M62">
         <v>1</v>
@@ -4087,101 +4104,101 @@
         <v>0</v>
       </c>
       <c r="O62">
-        <v>22.26</v>
+        <v>35.81</v>
       </c>
       <c r="P62" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S62" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="T62" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B63" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C63" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G63">
+        <v>49</v>
+      </c>
+      <c r="H63">
+        <v>3366.372093023256</v>
+      </c>
+      <c r="I63">
+        <v>242888.6744186046</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>39.53</v>
+      </c>
+      <c r="M63">
+        <v>1</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>35.81</v>
+      </c>
+      <c r="P63" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>60</v>
+      </c>
+      <c r="R63" t="s">
+        <v>61</v>
+      </c>
+      <c r="S63" t="s">
         <v>79</v>
       </c>
-      <c r="H63">
-        <v>189.2295081967213</v>
-      </c>
-      <c r="I63">
-        <v>1235122.38028169</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>19.9</v>
-      </c>
-      <c r="M63">
-        <v>1</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>27.96</v>
-      </c>
-      <c r="P63" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>59</v>
-      </c>
-      <c r="R63" t="s">
-        <v>60</v>
-      </c>
-      <c r="S63" t="s">
-        <v>70</v>
-      </c>
       <c r="T63" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C64" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G64">
-        <v>27</v>
+        <v>181</v>
       </c>
       <c r="H64">
-        <v>17.88888888888889</v>
+        <v>524.5260115606936</v>
       </c>
       <c r="I64">
-        <v>204634.5909090909</v>
+        <v>8888767.798449613</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -4190,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="L64">
-        <v>5.65</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="M64">
         <v>1</v>
@@ -4199,45 +4216,45 @@
         <v>0</v>
       </c>
       <c r="O64">
-        <v>22.26</v>
+        <v>46.74</v>
       </c>
       <c r="P64" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q64" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R64" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S64" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T64" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:20">
       <c r="A65" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B65" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C65" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D65" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G65">
-        <v>27</v>
+        <v>181</v>
       </c>
       <c r="H65">
-        <v>17.88888888888889</v>
+        <v>524.5260115606936</v>
       </c>
       <c r="I65">
-        <v>204634.5909090909</v>
+        <v>8888767.798449613</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4246,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>5.65</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="M65">
         <v>1</v>
@@ -4255,45 +4272,45 @@
         <v>0</v>
       </c>
       <c r="O65">
-        <v>22.26</v>
+        <v>46.74</v>
       </c>
       <c r="P65" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q65" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R65" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S65" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="T65" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:20">
       <c r="A66" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C66" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D66" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G66">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H66">
-        <v>17.88888888888889</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I66">
-        <v>204634.5909090909</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4302,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>5.65</v>
+        <v>39.53</v>
       </c>
       <c r="M66">
         <v>1</v>
@@ -4311,45 +4328,45 @@
         <v>0</v>
       </c>
       <c r="O66">
-        <v>22.26</v>
+        <v>35.81</v>
       </c>
       <c r="P66" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R66" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S66" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="T66" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C67" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D67" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G67">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="H67">
-        <v>17.88888888888889</v>
+        <v>589.8571428571429</v>
       </c>
       <c r="I67">
-        <v>204634.5909090909</v>
+        <v>8597932.334951457</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4358,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="L67">
-        <v>5.65</v>
+        <v>74.28</v>
       </c>
       <c r="M67">
         <v>1</v>
@@ -4367,45 +4384,45 @@
         <v>0</v>
       </c>
       <c r="O67">
-        <v>22.26</v>
+        <v>49.71</v>
       </c>
       <c r="P67" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q67" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R67" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S67" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="T67" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C68" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D68" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G68">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="H68">
-        <v>589.8571428571429</v>
+        <v>12.4</v>
       </c>
       <c r="I68">
-        <v>8597932.334951457</v>
+        <v>19377.6</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4414,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>74.28</v>
+        <v>3.91</v>
       </c>
       <c r="M68">
         <v>1</v>
@@ -4423,36 +4440,36 @@
         <v>0</v>
       </c>
       <c r="O68">
-        <v>49.71</v>
+        <v>21.56</v>
       </c>
       <c r="P68" t="s">
         <v>58</v>
       </c>
       <c r="Q68" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R68" t="s">
         <v>61</v>
       </c>
       <c r="S68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T68" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:20">
       <c r="A69" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B69" t="s">
         <v>45</v>
       </c>
       <c r="C69" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D69" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G69">
         <v>49</v>
@@ -4482,19 +4499,19 @@
         <v>35.81</v>
       </c>
       <c r="P69" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q69" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S69" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="T69" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:20">
@@ -4502,22 +4519,22 @@
         <v>26</v>
       </c>
       <c r="B70" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C70" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D70" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G70">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H70">
-        <v>3366.372093023256</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I70">
-        <v>242888.6744186046</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4526,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>39.53</v>
+        <v>5.65</v>
       </c>
       <c r="M70">
         <v>1</v>
@@ -4535,45 +4552,45 @@
         <v>0</v>
       </c>
       <c r="O70">
-        <v>35.81</v>
+        <v>22.26</v>
       </c>
       <c r="P70" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q70" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R70" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S70" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T70" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:20">
       <c r="A71" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B71" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C71" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D71" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G71">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="H71">
-        <v>589.8571428571429</v>
+        <v>189.2295081967213</v>
       </c>
       <c r="I71">
-        <v>8597932.334951457</v>
+        <v>1235122.38028169</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4582,7 +4599,7 @@
         <v>0</v>
       </c>
       <c r="L71">
-        <v>74.28</v>
+        <v>19.9</v>
       </c>
       <c r="M71">
         <v>1</v>
@@ -4591,22 +4608,22 @@
         <v>0</v>
       </c>
       <c r="O71">
-        <v>49.71</v>
+        <v>27.96</v>
       </c>
       <c r="P71" t="s">
         <v>58</v>
       </c>
       <c r="Q71" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R71" t="s">
         <v>61</v>
       </c>
       <c r="S71" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="T71" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -4614,22 +4631,22 @@
         <v>26</v>
       </c>
       <c r="B72" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C72" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D72" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G72">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H72">
-        <v>3366.372093023256</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I72">
-        <v>242888.6744186046</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4638,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>39.53</v>
+        <v>5.65</v>
       </c>
       <c r="M72">
         <v>1</v>
@@ -4647,45 +4664,45 @@
         <v>0</v>
       </c>
       <c r="O72">
-        <v>35.81</v>
+        <v>22.26</v>
       </c>
       <c r="P72" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q72" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R72" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S72" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="T72" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B73" t="s">
         <v>46</v>
       </c>
       <c r="C73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D73" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G73">
-        <v>225</v>
+        <v>27</v>
       </c>
       <c r="H73">
-        <v>589.8571428571429</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I73">
-        <v>8597932.334951457</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4694,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="L73">
-        <v>74.28</v>
+        <v>5.65</v>
       </c>
       <c r="M73">
         <v>1</v>
@@ -4703,22 +4720,22 @@
         <v>0</v>
       </c>
       <c r="O73">
-        <v>49.71</v>
+        <v>22.26</v>
       </c>
       <c r="P73" t="s">
         <v>58</v>
       </c>
       <c r="Q73" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R73" t="s">
         <v>61</v>
       </c>
       <c r="S73" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="T73" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -4726,22 +4743,22 @@
         <v>26</v>
       </c>
       <c r="B74" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C74" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D74" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G74">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H74">
-        <v>3366.372093023256</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I74">
-        <v>242888.6744186046</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4750,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>39.53</v>
+        <v>5.65</v>
       </c>
       <c r="M74">
         <v>1</v>
@@ -4759,22 +4776,22 @@
         <v>0</v>
       </c>
       <c r="O74">
-        <v>35.81</v>
+        <v>22.26</v>
       </c>
       <c r="P74" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R74" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S74" t="s">
         <v>70</v>
       </c>
       <c r="T74" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -4782,22 +4799,22 @@
         <v>26</v>
       </c>
       <c r="B75" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C75" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D75" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G75">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H75">
-        <v>3366.372093023256</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I75">
-        <v>242888.6744186046</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4806,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="L75">
-        <v>39.53</v>
+        <v>5.65</v>
       </c>
       <c r="M75">
         <v>1</v>
@@ -4815,45 +4832,45 @@
         <v>0</v>
       </c>
       <c r="O75">
-        <v>35.81</v>
+        <v>22.26</v>
       </c>
       <c r="P75" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q75" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R75" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S75" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T75" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C76" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D76" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G76">
-        <v>27</v>
+        <v>181</v>
       </c>
       <c r="H76">
-        <v>17.88888888888889</v>
+        <v>524.5260115606936</v>
       </c>
       <c r="I76">
-        <v>204634.5909090909</v>
+        <v>8888767.798449613</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4862,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>5.65</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="M76">
         <v>1</v>
@@ -4871,45 +4888,45 @@
         <v>0</v>
       </c>
       <c r="O76">
-        <v>22.26</v>
+        <v>46.74</v>
       </c>
       <c r="P76" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R76" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S76" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="T76" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C77" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D77" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G77">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="H77">
-        <v>3366.372093023256</v>
+        <v>589.8571428571429</v>
       </c>
       <c r="I77">
-        <v>242888.6744186046</v>
+        <v>8597932.334951457</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -4918,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="L77">
-        <v>39.53</v>
+        <v>74.28</v>
       </c>
       <c r="M77">
         <v>1</v>
@@ -4927,36 +4944,36 @@
         <v>0</v>
       </c>
       <c r="O77">
-        <v>35.81</v>
+        <v>49.71</v>
       </c>
       <c r="P77" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q77" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R77" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S77" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="T77" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B78" t="s">
         <v>45</v>
       </c>
       <c r="C78" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D78" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G78">
         <v>49</v>
@@ -4986,42 +5003,42 @@
         <v>35.81</v>
       </c>
       <c r="P78" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R78" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S78" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="T78" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B79" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C79" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D79" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G79">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H79">
-        <v>17.88888888888889</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I79">
-        <v>204634.5909090909</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -5030,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="L79">
-        <v>5.65</v>
+        <v>39.53</v>
       </c>
       <c r="M79">
         <v>1</v>
@@ -5039,45 +5056,45 @@
         <v>0</v>
       </c>
       <c r="O79">
-        <v>22.26</v>
+        <v>35.81</v>
       </c>
       <c r="P79" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q79" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R79" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S79" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="T79" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="1:20">
       <c r="A80" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B80" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C80" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D80" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G80">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="H80">
-        <v>17.88888888888889</v>
+        <v>589.8571428571429</v>
       </c>
       <c r="I80">
-        <v>204634.5909090909</v>
+        <v>8597932.334951457</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -5086,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>5.65</v>
+        <v>74.28</v>
       </c>
       <c r="M80">
         <v>1</v>
@@ -5095,36 +5112,36 @@
         <v>0</v>
       </c>
       <c r="O80">
-        <v>22.26</v>
+        <v>49.71</v>
       </c>
       <c r="P80" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R80" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S80" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="T80" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="81" spans="1:20">
       <c r="A81" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B81" t="s">
         <v>45</v>
       </c>
       <c r="C81" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D81" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G81">
         <v>49</v>
@@ -5154,42 +5171,42 @@
         <v>35.81</v>
       </c>
       <c r="P81" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R81" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S81" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T81" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82" spans="1:20">
       <c r="A82" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C82" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D82" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G82">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="H82">
-        <v>3366.372093023256</v>
+        <v>589.8571428571429</v>
       </c>
       <c r="I82">
-        <v>242888.6744186046</v>
+        <v>8597932.334951457</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -5198,7 +5215,7 @@
         <v>0</v>
       </c>
       <c r="L82">
-        <v>39.53</v>
+        <v>74.28</v>
       </c>
       <c r="M82">
         <v>1</v>
@@ -5207,42 +5224,45 @@
         <v>0</v>
       </c>
       <c r="O82">
-        <v>35.81</v>
+        <v>49.71</v>
       </c>
       <c r="P82" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R82" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S82" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T82" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="83" spans="1:20">
       <c r="A83" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B83" t="s">
+        <v>45</v>
       </c>
       <c r="C83" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D83" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I83">
-        <v>0</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -5251,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="L83">
-        <v>0</v>
+        <v>39.53</v>
       </c>
       <c r="M83">
         <v>1</v>
@@ -5260,42 +5280,45 @@
         <v>0</v>
       </c>
       <c r="O83">
-        <v>20</v>
+        <v>35.81</v>
       </c>
       <c r="P83" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R83" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S83" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="T83" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="84" spans="1:20">
       <c r="A84" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B84" t="s">
+        <v>45</v>
       </c>
       <c r="C84" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D84" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I84">
-        <v>0</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -5304,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>39.53</v>
       </c>
       <c r="M84">
         <v>1</v>
@@ -5313,42 +5336,45 @@
         <v>0</v>
       </c>
       <c r="O84">
-        <v>20</v>
+        <v>35.81</v>
       </c>
       <c r="P84" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q84" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R84" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S84" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T84" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" spans="1:20">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="B85" t="s">
+        <v>46</v>
       </c>
       <c r="C85" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D85" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -5357,7 +5383,7 @@
         <v>0</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="M85">
         <v>1</v>
@@ -5366,42 +5392,45 @@
         <v>0</v>
       </c>
       <c r="O85">
-        <v>20</v>
+        <v>22.26</v>
       </c>
       <c r="P85" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q85" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R85" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S85" t="s">
         <v>77</v>
       </c>
       <c r="T85" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="86" spans="1:20">
       <c r="A86" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B86" t="s">
+        <v>45</v>
       </c>
       <c r="C86" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D86" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -5410,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>39.53</v>
       </c>
       <c r="M86">
         <v>1</v>
@@ -5419,42 +5448,45 @@
         <v>0</v>
       </c>
       <c r="O86">
-        <v>20</v>
+        <v>35.81</v>
       </c>
       <c r="P86" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q86" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R86" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S86" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T86" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87" spans="1:20">
       <c r="A87" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="B87" t="s">
+        <v>47</v>
       </c>
       <c r="C87" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D87" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>524.5260115606936</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>8888767.798449613</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5463,7 +5495,7 @@
         <v>0</v>
       </c>
       <c r="L87">
-        <v>0</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="M87">
         <v>1</v>
@@ -5472,42 +5504,45 @@
         <v>0</v>
       </c>
       <c r="O87">
-        <v>20</v>
+        <v>46.74</v>
       </c>
       <c r="P87" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q87" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R87" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S87" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="T87" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="1:20">
       <c r="A88" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B88" t="s">
+        <v>45</v>
       </c>
       <c r="C88" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D88" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I88">
-        <v>0</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5516,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>39.53</v>
       </c>
       <c r="M88">
         <v>1</v>
@@ -5525,42 +5560,45 @@
         <v>0</v>
       </c>
       <c r="O88">
-        <v>20</v>
+        <v>35.81</v>
       </c>
       <c r="P88" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q88" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R88" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S88" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="T88" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:20">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="B89" t="s">
+        <v>46</v>
       </c>
       <c r="C89" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I89">
-        <v>0</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5569,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="L89">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="M89">
         <v>1</v>
@@ -5578,42 +5616,45 @@
         <v>0</v>
       </c>
       <c r="O89">
-        <v>20</v>
+        <v>22.26</v>
       </c>
       <c r="P89" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q89" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R89" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S89" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="T89" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:20">
       <c r="A90" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="B90" t="s">
+        <v>46</v>
       </c>
       <c r="C90" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>17.88888888888889</v>
       </c>
       <c r="I90">
-        <v>0</v>
+        <v>204634.5909090909</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5622,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="L90">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="M90">
         <v>1</v>
@@ -5631,42 +5672,45 @@
         <v>0</v>
       </c>
       <c r="O90">
-        <v>20</v>
+        <v>22.26</v>
       </c>
       <c r="P90" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q90" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R90" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S90" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="T90" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:20">
       <c r="A91" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B91" t="s">
+        <v>45</v>
       </c>
       <c r="C91" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D91" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I91">
-        <v>0</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5675,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="L91">
-        <v>0</v>
+        <v>39.53</v>
       </c>
       <c r="M91">
         <v>1</v>
@@ -5684,42 +5728,45 @@
         <v>0</v>
       </c>
       <c r="O91">
-        <v>20</v>
+        <v>35.81</v>
       </c>
       <c r="P91" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q91" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R91" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S91" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T91" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:20">
       <c r="A92" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B92" t="s">
+        <v>45</v>
       </c>
       <c r="C92" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D92" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H92">
-        <v>0</v>
+        <v>3366.372093023256</v>
       </c>
       <c r="I92">
-        <v>0</v>
+        <v>242888.6744186046</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5728,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="L92">
-        <v>0</v>
+        <v>39.53</v>
       </c>
       <c r="M92">
         <v>1</v>
@@ -5737,33 +5784,33 @@
         <v>0</v>
       </c>
       <c r="O92">
-        <v>20</v>
+        <v>35.81</v>
       </c>
       <c r="P92" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R92" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S92" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T92" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="93" spans="1:20">
       <c r="A93" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C93" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D93" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -5793,30 +5840,30 @@
         <v>20</v>
       </c>
       <c r="P93" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q93" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R93" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S93" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T93" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:20">
       <c r="A94" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C94" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -5846,30 +5893,30 @@
         <v>20</v>
       </c>
       <c r="P94" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q94" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R94" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S94" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T94" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:20">
       <c r="A95" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C95" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D95" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -5899,30 +5946,30 @@
         <v>20</v>
       </c>
       <c r="P95" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q95" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R95" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S95" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T95" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:20">
       <c r="A96" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C96" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D96" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -5952,30 +5999,30 @@
         <v>20</v>
       </c>
       <c r="P96" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q96" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R96" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S96" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T96" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="1:20">
       <c r="A97" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C97" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D97" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -6005,30 +6052,30 @@
         <v>20</v>
       </c>
       <c r="P97" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q97" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R97" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S97" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T97" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98" spans="1:20">
       <c r="A98" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C98" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D98" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -6058,30 +6105,30 @@
         <v>20</v>
       </c>
       <c r="P98" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q98" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R98" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S98" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T98" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99" spans="1:20">
       <c r="A99" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C99" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D99" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -6111,30 +6158,30 @@
         <v>20</v>
       </c>
       <c r="P99" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q99" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R99" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S99" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T99" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:20">
       <c r="A100" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C100" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D100" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -6164,30 +6211,30 @@
         <v>20</v>
       </c>
       <c r="P100" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q100" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R100" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S100" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T100" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="1:20">
       <c r="A101" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C101" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D101" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -6217,30 +6264,30 @@
         <v>20</v>
       </c>
       <c r="P101" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R101" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S101" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T101" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="102" spans="1:20">
       <c r="A102" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C102" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D102" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -6270,30 +6317,30 @@
         <v>20</v>
       </c>
       <c r="P102" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q102" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R102" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S102" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T102" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103" spans="1:20">
       <c r="A103" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C103" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D103" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -6323,30 +6370,30 @@
         <v>20</v>
       </c>
       <c r="P103" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q103" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R103" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S103" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T103" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="104" spans="1:20">
       <c r="A104" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C104" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D104" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -6376,30 +6423,30 @@
         <v>20</v>
       </c>
       <c r="P104" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q104" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R104" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S104" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T104" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="105" spans="1:20">
       <c r="A105" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C105" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D105" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -6429,30 +6476,30 @@
         <v>20</v>
       </c>
       <c r="P105" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q105" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R105" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S105" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T105" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="106" spans="1:20">
       <c r="A106" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C106" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D106" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -6482,30 +6529,30 @@
         <v>20</v>
       </c>
       <c r="P106" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q106" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R106" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S106" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T106" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="107" spans="1:20">
       <c r="A107" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C107" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D107" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -6535,42 +6582,39 @@
         <v>20</v>
       </c>
       <c r="P107" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q107" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R107" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S107" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T107" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="108" spans="1:20">
       <c r="A108" t="s">
-        <v>31</v>
-      </c>
-      <c r="B108" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C108" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D108" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G108">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H108">
-        <v>1506.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I108">
-        <v>319805.8027210885</v>
+        <v>0</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -6579,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="L108">
-        <v>42.24</v>
+        <v>0</v>
       </c>
       <c r="M108">
         <v>1</v>
@@ -6588,33 +6632,33 @@
         <v>0</v>
       </c>
       <c r="O108">
-        <v>36.89</v>
+        <v>20</v>
       </c>
       <c r="P108" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q108" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R108" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S108" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="T108" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="109" spans="1:20">
       <c r="A109" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C109" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D109" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -6644,30 +6688,30 @@
         <v>20</v>
       </c>
       <c r="P109" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q109" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R109" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S109" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T109" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="110" spans="1:20">
       <c r="A110" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C110" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D110" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -6697,30 +6741,30 @@
         <v>20</v>
       </c>
       <c r="P110" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q110" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R110" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="111" spans="1:20">
       <c r="A111" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C111" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D111" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -6750,30 +6794,30 @@
         <v>20</v>
       </c>
       <c r="P111" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q111" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R111" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S111" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T111" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="112" spans="1:20">
       <c r="A112" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C112" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D112" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -6803,30 +6847,30 @@
         <v>20</v>
       </c>
       <c r="P112" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q112" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R112" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S112" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T112" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="113" spans="1:20">
       <c r="A113" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C113" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D113" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -6856,30 +6900,30 @@
         <v>20</v>
       </c>
       <c r="P113" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q113" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R113" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S113" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T113" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="114" spans="1:20">
       <c r="A114" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C114" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -6909,30 +6953,30 @@
         <v>20</v>
       </c>
       <c r="P114" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q114" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R114" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S114" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T114" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="115" spans="1:20">
       <c r="A115" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C115" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D115" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -6962,30 +7006,30 @@
         <v>20</v>
       </c>
       <c r="P115" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q115" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R115" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S115" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T115" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="116" spans="1:20">
       <c r="A116" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C116" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D116" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -7015,30 +7059,30 @@
         <v>20</v>
       </c>
       <c r="P116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q116" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R116" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S116" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T116" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="117" spans="1:20">
       <c r="A117" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C117" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D117" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -7068,39 +7112,42 @@
         <v>20</v>
       </c>
       <c r="P117" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R117" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S117" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T117" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="118" spans="1:20">
       <c r="A118" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="B118" t="s">
+        <v>52</v>
       </c>
       <c r="C118" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D118" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>1506.333333333333</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>319805.8027210885</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -7109,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="L118">
-        <v>0</v>
+        <v>42.24</v>
       </c>
       <c r="M118">
         <v>1</v>
@@ -7118,33 +7165,33 @@
         <v>0</v>
       </c>
       <c r="O118">
-        <v>20</v>
+        <v>36.89</v>
       </c>
       <c r="P118" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q118" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R118" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S118" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T118" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="119" spans="1:20">
       <c r="A119" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C119" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D119" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -7174,30 +7221,30 @@
         <v>20</v>
       </c>
       <c r="P119" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R119" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S119" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T119" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="120" spans="1:20">
       <c r="A120" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C120" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D120" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -7227,30 +7274,30 @@
         <v>20</v>
       </c>
       <c r="P120" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q120" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R120" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S120" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T120" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="121" spans="1:20">
       <c r="A121" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C121" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D121" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -7280,30 +7327,30 @@
         <v>20</v>
       </c>
       <c r="P121" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q121" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S121" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T121" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="122" spans="1:20">
       <c r="A122" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C122" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D122" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -7333,30 +7380,30 @@
         <v>20</v>
       </c>
       <c r="P122" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q122" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R122" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S122" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T122" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="123" spans="1:20">
       <c r="A123" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C123" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D123" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -7386,30 +7433,30 @@
         <v>20</v>
       </c>
       <c r="P123" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q123" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R123" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S123" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T123" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="124" spans="1:20">
       <c r="A124" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C124" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D124" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -7439,30 +7486,30 @@
         <v>20</v>
       </c>
       <c r="P124" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q124" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R124" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S124" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T124" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="125" spans="1:20">
       <c r="A125" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C125" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D125" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -7492,30 +7539,30 @@
         <v>20</v>
       </c>
       <c r="P125" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q125" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R125" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S125" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T125" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="126" spans="1:20">
       <c r="A126" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C126" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D126" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -7545,30 +7592,30 @@
         <v>20</v>
       </c>
       <c r="P126" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q126" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R126" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S126" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T126" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="127" spans="1:20">
       <c r="A127" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C127" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D127" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -7598,30 +7645,30 @@
         <v>20</v>
       </c>
       <c r="P127" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q127" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R127" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S127" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T127" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="128" spans="1:20">
       <c r="A128" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C128" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D128" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -7651,30 +7698,30 @@
         <v>20</v>
       </c>
       <c r="P128" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q128" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R128" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S128" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T128" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="129" spans="1:20">
       <c r="A129" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C129" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D129" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -7704,30 +7751,30 @@
         <v>20</v>
       </c>
       <c r="P129" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q129" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R129" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S129" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T129" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="130" spans="1:20">
       <c r="A130" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C130" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D130" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -7757,30 +7804,30 @@
         <v>20</v>
       </c>
       <c r="P130" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q130" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R130" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S130" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T130" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="131" spans="1:20">
       <c r="A131" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C131" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D131" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -7810,30 +7857,30 @@
         <v>20</v>
       </c>
       <c r="P131" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q131" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R131" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S131" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T131" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="132" spans="1:20">
       <c r="A132" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C132" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D132" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -7863,30 +7910,30 @@
         <v>20</v>
       </c>
       <c r="P132" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q132" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R132" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S132" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T132" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="133" spans="1:20">
       <c r="A133" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C133" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D133" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -7916,42 +7963,39 @@
         <v>20</v>
       </c>
       <c r="P133" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q133" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R133" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S133" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T133" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="134" spans="1:20">
       <c r="A134" t="s">
-        <v>33</v>
-      </c>
-      <c r="B134" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C134" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D134" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G134">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H134">
-        <v>32.4074074074074</v>
+        <v>0</v>
       </c>
       <c r="I134">
-        <v>212236.9315068493</v>
+        <v>0</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -7960,7 +8004,7 @@
         <v>0</v>
       </c>
       <c r="L134">
-        <v>17.36</v>
+        <v>0</v>
       </c>
       <c r="M134">
         <v>1</v>
@@ -7969,45 +8013,42 @@
         <v>0</v>
       </c>
       <c r="O134">
-        <v>26.94</v>
+        <v>20</v>
       </c>
       <c r="P134" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q134" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R134" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S134" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="T134" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="135" spans="1:20">
       <c r="A135" t="s">
-        <v>33</v>
-      </c>
-      <c r="B135" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C135" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D135" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G135">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H135">
-        <v>32.4074074074074</v>
+        <v>0</v>
       </c>
       <c r="I135">
-        <v>212236.9315068493</v>
+        <v>0</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -8016,7 +8057,7 @@
         <v>0</v>
       </c>
       <c r="L135">
-        <v>17.36</v>
+        <v>0</v>
       </c>
       <c r="M135">
         <v>1</v>
@@ -8025,45 +8066,42 @@
         <v>0</v>
       </c>
       <c r="O135">
-        <v>26.94</v>
+        <v>20</v>
       </c>
       <c r="P135" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q135" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R135" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S135" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T135" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="136" spans="1:20">
       <c r="A136" t="s">
-        <v>33</v>
-      </c>
-      <c r="B136" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C136" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D136" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G136">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H136">
-        <v>32.4074074074074</v>
+        <v>0</v>
       </c>
       <c r="I136">
-        <v>212236.9315068493</v>
+        <v>0</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -8072,7 +8110,7 @@
         <v>0</v>
       </c>
       <c r="L136">
-        <v>17.36</v>
+        <v>0</v>
       </c>
       <c r="M136">
         <v>1</v>
@@ -8081,16 +8119,16 @@
         <v>0</v>
       </c>
       <c r="O136">
-        <v>26.94</v>
+        <v>20</v>
       </c>
       <c r="P136" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q136" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R136" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S136" t="s">
         <v>82</v>
@@ -8101,13 +8139,13 @@
     </row>
     <row r="137" spans="1:20">
       <c r="A137" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C137" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D137" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -8137,30 +8175,30 @@
         <v>20</v>
       </c>
       <c r="P137" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q137" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R137" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S137" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T137" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="138" spans="1:20">
       <c r="A138" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C138" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D138" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -8190,30 +8228,30 @@
         <v>20</v>
       </c>
       <c r="P138" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q138" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R138" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S138" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T138" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="139" spans="1:20">
       <c r="A139" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C139" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D139" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -8243,30 +8281,30 @@
         <v>20</v>
       </c>
       <c r="P139" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R139" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S139" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T139" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="140" spans="1:20">
       <c r="A140" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C140" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D140" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -8296,30 +8334,30 @@
         <v>20</v>
       </c>
       <c r="P140" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q140" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R140" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S140" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T140" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="141" spans="1:20">
       <c r="A141" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C141" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D141" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -8349,30 +8387,30 @@
         <v>20</v>
       </c>
       <c r="P141" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q141" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R141" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S141" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T141" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="142" spans="1:20">
       <c r="A142" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C142" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D142" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -8402,30 +8440,30 @@
         <v>20</v>
       </c>
       <c r="P142" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q142" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R142" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S142" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T142" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="143" spans="1:20">
       <c r="A143" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C143" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D143" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -8455,39 +8493,42 @@
         <v>20</v>
       </c>
       <c r="P143" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q143" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R143" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S143" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T143" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="144" spans="1:20">
       <c r="A144" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="B144" t="s">
+        <v>53</v>
       </c>
       <c r="C144" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D144" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>32.4074074074074</v>
       </c>
       <c r="I144">
-        <v>0</v>
+        <v>212236.9315068493</v>
       </c>
       <c r="J144">
         <v>0</v>
@@ -8496,7 +8537,7 @@
         <v>0</v>
       </c>
       <c r="L144">
-        <v>0</v>
+        <v>17.36</v>
       </c>
       <c r="M144">
         <v>1</v>
@@ -8505,16 +8546,16 @@
         <v>0</v>
       </c>
       <c r="O144">
-        <v>20</v>
+        <v>26.94</v>
       </c>
       <c r="P144" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q144" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R144" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S144" t="s">
         <v>83</v>
@@ -8525,22 +8566,25 @@
     </row>
     <row r="145" spans="1:20">
       <c r="A145" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="B145" t="s">
+        <v>53</v>
       </c>
       <c r="C145" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D145" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>32.4074074074074</v>
       </c>
       <c r="I145">
-        <v>0</v>
+        <v>212236.9315068493</v>
       </c>
       <c r="J145">
         <v>0</v>
@@ -8549,7 +8593,7 @@
         <v>0</v>
       </c>
       <c r="L145">
-        <v>0</v>
+        <v>17.36</v>
       </c>
       <c r="M145">
         <v>1</v>
@@ -8558,42 +8602,45 @@
         <v>0</v>
       </c>
       <c r="O145">
-        <v>20</v>
+        <v>26.94</v>
       </c>
       <c r="P145" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q145" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R145" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S145" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T145" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="146" spans="1:20">
       <c r="A146" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="B146" t="s">
+        <v>53</v>
       </c>
       <c r="C146" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D146" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>32.4074074074074</v>
       </c>
       <c r="I146">
-        <v>0</v>
+        <v>212236.9315068493</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -8602,7 +8649,7 @@
         <v>0</v>
       </c>
       <c r="L146">
-        <v>0</v>
+        <v>17.36</v>
       </c>
       <c r="M146">
         <v>1</v>
@@ -8611,33 +8658,33 @@
         <v>0</v>
       </c>
       <c r="O146">
-        <v>20</v>
+        <v>26.94</v>
       </c>
       <c r="P146" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q146" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R146" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S146" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="T146" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="147" spans="1:20">
       <c r="A147" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C147" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D147" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -8667,30 +8714,30 @@
         <v>20</v>
       </c>
       <c r="P147" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q147" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R147" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S147" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T147" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="148" spans="1:20">
       <c r="A148" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C148" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D148" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -8720,30 +8767,30 @@
         <v>20</v>
       </c>
       <c r="P148" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q148" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R148" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S148" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T148" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="149" spans="1:20">
       <c r="A149" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C149" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D149" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -8773,30 +8820,30 @@
         <v>20</v>
       </c>
       <c r="P149" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q149" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R149" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S149" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T149" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="150" spans="1:20">
       <c r="A150" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C150" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D150" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -8826,30 +8873,30 @@
         <v>20</v>
       </c>
       <c r="P150" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q150" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R150" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S150" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T150" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="151" spans="1:20">
       <c r="A151" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C151" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D151" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -8879,30 +8926,30 @@
         <v>20</v>
       </c>
       <c r="P151" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q151" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R151" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S151" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T151" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="152" spans="1:20">
       <c r="A152" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C152" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D152" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -8932,30 +8979,30 @@
         <v>20</v>
       </c>
       <c r="P152" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q152" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R152" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S152" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T152" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="153" spans="1:20">
       <c r="A153" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C153" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D153" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -8985,30 +9032,30 @@
         <v>20</v>
       </c>
       <c r="P153" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q153" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R153" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S153" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T153" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="154" spans="1:20">
       <c r="A154" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C154" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D154" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -9038,30 +9085,30 @@
         <v>20</v>
       </c>
       <c r="P154" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q154" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R154" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S154" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T154" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="155" spans="1:20">
       <c r="A155" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C155" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D155" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -9091,30 +9138,30 @@
         <v>20</v>
       </c>
       <c r="P155" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q155" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R155" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S155" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T155" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="156" spans="1:20">
       <c r="A156" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C156" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D156" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -9144,30 +9191,30 @@
         <v>20</v>
       </c>
       <c r="P156" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q156" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R156" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S156" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T156" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="157" spans="1:20">
       <c r="A157" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C157" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D157" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -9197,30 +9244,30 @@
         <v>20</v>
       </c>
       <c r="P157" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q157" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R157" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S157" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T157" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="158" spans="1:20">
       <c r="A158" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C158" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D158" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -9250,30 +9297,30 @@
         <v>20</v>
       </c>
       <c r="P158" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q158" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R158" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S158" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T158" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="159" spans="1:20">
       <c r="A159" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C159" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D159" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -9303,30 +9350,30 @@
         <v>20</v>
       </c>
       <c r="P159" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q159" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R159" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S159" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T159" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="160" spans="1:20">
       <c r="A160" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C160" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D160" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G160">
         <v>0</v>
@@ -9356,30 +9403,30 @@
         <v>20</v>
       </c>
       <c r="P160" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q160" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R160" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S160" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T160" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="161" spans="1:20">
       <c r="A161" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C161" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D161" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G161">
         <v>0</v>
@@ -9409,42 +9456,39 @@
         <v>20</v>
       </c>
       <c r="P161" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q161" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R161" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S161" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T161" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="162" spans="1:20">
       <c r="A162" t="s">
-        <v>35</v>
-      </c>
-      <c r="B162" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C162" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D162" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G162">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H162">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="I162">
-        <v>28148.625</v>
+        <v>0</v>
       </c>
       <c r="J162">
         <v>0</v>
@@ -9453,7 +9497,7 @@
         <v>0</v>
       </c>
       <c r="L162">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M162">
         <v>1</v>
@@ -9462,45 +9506,42 @@
         <v>0</v>
       </c>
       <c r="O162">
-        <v>20.76</v>
+        <v>20</v>
       </c>
       <c r="P162" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q162" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R162" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S162" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T162" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="163" spans="1:20">
       <c r="A163" t="s">
-        <v>31</v>
-      </c>
-      <c r="B163" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C163" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D163" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G163">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>1506.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I163">
-        <v>319805.8027210885</v>
+        <v>0</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -9509,7 +9550,7 @@
         <v>0</v>
       </c>
       <c r="L163">
-        <v>42.24</v>
+        <v>0</v>
       </c>
       <c r="M163">
         <v>1</v>
@@ -9518,45 +9559,42 @@
         <v>0</v>
       </c>
       <c r="O163">
-        <v>36.89</v>
+        <v>20</v>
       </c>
       <c r="P163" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q163" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R163" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S163" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T163" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="164" spans="1:20">
       <c r="A164" t="s">
-        <v>33</v>
-      </c>
-      <c r="B164" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C164" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D164" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G164">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H164">
-        <v>32.4074074074074</v>
+        <v>0</v>
       </c>
       <c r="I164">
-        <v>212236.9315068493</v>
+        <v>0</v>
       </c>
       <c r="J164">
         <v>0</v>
@@ -9565,7 +9603,7 @@
         <v>0</v>
       </c>
       <c r="L164">
-        <v>17.36</v>
+        <v>0</v>
       </c>
       <c r="M164">
         <v>1</v>
@@ -9574,16 +9612,16 @@
         <v>0</v>
       </c>
       <c r="O164">
-        <v>26.94</v>
+        <v>20</v>
       </c>
       <c r="P164" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q164" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R164" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S164" t="s">
         <v>86</v>
@@ -9594,25 +9632,22 @@
     </row>
     <row r="165" spans="1:20">
       <c r="A165" t="s">
-        <v>33</v>
-      </c>
-      <c r="B165" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C165" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D165" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G165">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>32.4074074074074</v>
+        <v>0</v>
       </c>
       <c r="I165">
-        <v>212236.9315068493</v>
+        <v>0</v>
       </c>
       <c r="J165">
         <v>0</v>
@@ -9621,7 +9656,7 @@
         <v>0</v>
       </c>
       <c r="L165">
-        <v>17.36</v>
+        <v>0</v>
       </c>
       <c r="M165">
         <v>1</v>
@@ -9630,45 +9665,42 @@
         <v>0</v>
       </c>
       <c r="O165">
-        <v>26.94</v>
+        <v>20</v>
       </c>
       <c r="P165" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q165" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R165" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S165" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T165" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="166" spans="1:20">
       <c r="A166" t="s">
-        <v>36</v>
-      </c>
-      <c r="B166" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C166" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D166" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G166">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>258.11</v>
+        <v>0</v>
       </c>
       <c r="I166">
-        <v>1947843.212598425</v>
+        <v>0</v>
       </c>
       <c r="J166">
         <v>0</v>
@@ -9677,7 +9709,7 @@
         <v>0</v>
       </c>
       <c r="L166">
-        <v>31.99</v>
+        <v>0</v>
       </c>
       <c r="M166">
         <v>1</v>
@@ -9686,45 +9718,42 @@
         <v>0</v>
       </c>
       <c r="O166">
-        <v>32.79</v>
+        <v>20</v>
       </c>
       <c r="P166" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q166" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R166" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S166" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="T166" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="167" spans="1:20">
       <c r="A167" t="s">
-        <v>37</v>
-      </c>
-      <c r="B167" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C167" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D167" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G167">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>872.1941747572815</v>
+        <v>0</v>
       </c>
       <c r="I167">
-        <v>1302413.493670886</v>
+        <v>0</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -9733,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="L167">
-        <v>31.01</v>
+        <v>0</v>
       </c>
       <c r="M167">
         <v>1</v>
@@ -9742,45 +9771,42 @@
         <v>0</v>
       </c>
       <c r="O167">
-        <v>32.41</v>
+        <v>20</v>
       </c>
       <c r="P167" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q167" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R167" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S167" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T167" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="168" spans="1:20">
       <c r="A168" t="s">
-        <v>23</v>
-      </c>
-      <c r="B168" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C168" t="s">
         <v>55</v>
       </c>
       <c r="D168" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G168">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H168">
-        <v>189.2295081967213</v>
+        <v>0</v>
       </c>
       <c r="I168">
-        <v>1235122.38028169</v>
+        <v>0</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -9789,7 +9815,7 @@
         <v>0</v>
       </c>
       <c r="L168">
-        <v>19.9</v>
+        <v>0</v>
       </c>
       <c r="M168">
         <v>1</v>
@@ -9798,45 +9824,42 @@
         <v>0</v>
       </c>
       <c r="O168">
-        <v>27.96</v>
+        <v>20</v>
       </c>
       <c r="P168" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q168" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R168" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S168" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="T168" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="169" spans="1:20">
       <c r="A169" t="s">
-        <v>28</v>
-      </c>
-      <c r="B169" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C169" t="s">
         <v>55</v>
       </c>
       <c r="D169" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G169">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>589.8571428571429</v>
+        <v>0</v>
       </c>
       <c r="I169">
-        <v>8597932.334951457</v>
+        <v>0</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -9845,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="L169">
-        <v>74.28</v>
+        <v>0</v>
       </c>
       <c r="M169">
         <v>1</v>
@@ -9854,45 +9877,42 @@
         <v>0</v>
       </c>
       <c r="O169">
-        <v>49.71</v>
+        <v>20</v>
       </c>
       <c r="P169" t="s">
         <v>58</v>
       </c>
       <c r="Q169" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R169" t="s">
         <v>61</v>
       </c>
       <c r="S169" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="T169" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="170" spans="1:20">
       <c r="A170" t="s">
         <v>38</v>
       </c>
-      <c r="B170" t="s">
-        <v>53</v>
-      </c>
       <c r="C170" t="s">
         <v>55</v>
       </c>
       <c r="D170" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G170">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="H170">
-        <v>524.5260115606936</v>
+        <v>0</v>
       </c>
       <c r="I170">
-        <v>8888767.798449613</v>
+        <v>0</v>
       </c>
       <c r="J170">
         <v>0</v>
@@ -9901,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="L170">
-        <v>66.84999999999999</v>
+        <v>0</v>
       </c>
       <c r="M170">
         <v>1</v>
@@ -9910,45 +9930,42 @@
         <v>0</v>
       </c>
       <c r="O170">
-        <v>46.74</v>
+        <v>20</v>
       </c>
       <c r="P170" t="s">
         <v>58</v>
       </c>
       <c r="Q170" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R170" t="s">
         <v>61</v>
       </c>
       <c r="S170" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="T170" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="171" spans="1:20">
       <c r="A171" t="s">
-        <v>28</v>
-      </c>
-      <c r="B171" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C171" t="s">
         <v>55</v>
       </c>
       <c r="D171" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G171">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>589.8571428571429</v>
+        <v>0</v>
       </c>
       <c r="I171">
-        <v>8597932.334951457</v>
+        <v>0</v>
       </c>
       <c r="J171">
         <v>0</v>
@@ -9957,7 +9974,7 @@
         <v>0</v>
       </c>
       <c r="L171">
-        <v>74.28</v>
+        <v>0</v>
       </c>
       <c r="M171">
         <v>1</v>
@@ -9966,45 +9983,45 @@
         <v>0</v>
       </c>
       <c r="O171">
-        <v>49.71</v>
+        <v>20</v>
       </c>
       <c r="P171" t="s">
         <v>58</v>
       </c>
       <c r="Q171" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R171" t="s">
         <v>61</v>
       </c>
       <c r="S171" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="T171" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="172" spans="1:20">
       <c r="A172" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B172" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C172" t="s">
         <v>55</v>
       </c>
       <c r="D172" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G172">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="H172">
-        <v>3366.372093023256</v>
+        <v>4.25</v>
       </c>
       <c r="I172">
-        <v>242888.6744186046</v>
+        <v>28148.625</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -10013,7 +10030,7 @@
         <v>0</v>
       </c>
       <c r="L172">
-        <v>39.53</v>
+        <v>1.91</v>
       </c>
       <c r="M172">
         <v>1</v>
@@ -10022,45 +10039,45 @@
         <v>0</v>
       </c>
       <c r="O172">
-        <v>35.81</v>
+        <v>20.76</v>
       </c>
       <c r="P172" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q172" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R172" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S172" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="T172" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="173" spans="1:20">
       <c r="A173" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B173" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C173" t="s">
         <v>55</v>
       </c>
       <c r="D173" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G173">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c r="H173">
-        <v>3366.372093023256</v>
+        <v>1506.333333333333</v>
       </c>
       <c r="I173">
-        <v>242888.6744186046</v>
+        <v>319805.8027210885</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -10069,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="L173">
-        <v>39.53</v>
+        <v>42.24</v>
       </c>
       <c r="M173">
         <v>1</v>
@@ -10078,22 +10095,22 @@
         <v>0</v>
       </c>
       <c r="O173">
-        <v>35.81</v>
+        <v>36.89</v>
       </c>
       <c r="P173" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q173" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R173" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S173" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="T173" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/latest_scorecard.xlsx
+++ b/data/outputs/latest_scorecard.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="88">
   <si>
     <t>country</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>Kazakhstan</t>
+  </si>
+  <si>
+    <t>UNK</t>
   </si>
   <si>
     <t>PNG</t>
@@ -687,11 +690,14 @@
       <c r="A2" t="s">
         <v>24</v>
       </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -736,33 +742,36 @@
         <v>313920</v>
       </c>
       <c r="S2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" t="s">
         <v>24</v>
       </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -807,33 +816,36 @@
         <v>313920</v>
       </c>
       <c r="S3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" t="s">
         <v>24</v>
       </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -878,33 +890,36 @@
         <v>313920</v>
       </c>
       <c r="S4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" t="s">
         <v>24</v>
       </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -949,33 +964,36 @@
         <v>313920</v>
       </c>
       <c r="S5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" t="s">
         <v>24</v>
       </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1020,33 +1038,36 @@
         <v>313920</v>
       </c>
       <c r="S6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" t="s">
         <v>24</v>
       </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1091,33 +1112,36 @@
         <v>313920</v>
       </c>
       <c r="S7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" t="s">
         <v>24</v>
       </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1162,33 +1186,36 @@
         <v>313920</v>
       </c>
       <c r="S8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>24</v>
       </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1233,33 +1260,36 @@
         <v>313920</v>
       </c>
       <c r="S9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" t="s">
         <v>24</v>
       </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1304,33 +1334,36 @@
         <v>313920</v>
       </c>
       <c r="S10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>24</v>
       </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1375,33 +1408,36 @@
         <v>313920</v>
       </c>
       <c r="S11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:24">
       <c r="A12" t="s">
         <v>24</v>
       </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1446,33 +1482,36 @@
         <v>313920</v>
       </c>
       <c r="S12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>24</v>
       </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1517,33 +1556,36 @@
         <v>313920</v>
       </c>
       <c r="S13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:24">
       <c r="A14" t="s">
         <v>24</v>
       </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1588,33 +1630,36 @@
         <v>313920</v>
       </c>
       <c r="S14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:24">
       <c r="A15" t="s">
         <v>24</v>
       </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1659,33 +1704,36 @@
         <v>313920</v>
       </c>
       <c r="S15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:24">
       <c r="A16" t="s">
         <v>24</v>
       </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1730,33 +1778,36 @@
         <v>313920</v>
       </c>
       <c r="S16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:24">
       <c r="A17" t="s">
         <v>24</v>
       </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1801,33 +1852,36 @@
         <v>313920</v>
       </c>
       <c r="S17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:24">
       <c r="A18" t="s">
         <v>24</v>
       </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1872,33 +1926,36 @@
         <v>313920</v>
       </c>
       <c r="S18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:24">
       <c r="A19" t="s">
         <v>24</v>
       </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1943,33 +2000,36 @@
         <v>313920</v>
       </c>
       <c r="S19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:24">
       <c r="A20" t="s">
         <v>24</v>
       </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2014,33 +2074,36 @@
         <v>313920</v>
       </c>
       <c r="S20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:24">
       <c r="A21" t="s">
         <v>24</v>
       </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2085,33 +2148,36 @@
         <v>313920</v>
       </c>
       <c r="S21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:24">
       <c r="A22" t="s">
         <v>24</v>
       </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2156,33 +2222,36 @@
         <v>313920</v>
       </c>
       <c r="S22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:24">
       <c r="A23" t="s">
         <v>24</v>
       </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2227,33 +2296,36 @@
         <v>313920</v>
       </c>
       <c r="S23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:24">
       <c r="A24" t="s">
         <v>24</v>
       </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2298,33 +2370,36 @@
         <v>313920</v>
       </c>
       <c r="S24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:24">
       <c r="A25" t="s">
         <v>24</v>
       </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2369,33 +2444,36 @@
         <v>313920</v>
       </c>
       <c r="S25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:24">
       <c r="A26" t="s">
         <v>24</v>
       </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2440,22 +2518,22 @@
         <v>313920</v>
       </c>
       <c r="S26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:24">
@@ -2463,13 +2541,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2514,22 +2592,22 @@
         <v>20472280</v>
       </c>
       <c r="S27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:24">
@@ -2537,13 +2615,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2588,22 +2666,22 @@
         <v>58760</v>
       </c>
       <c r="S28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:24">
@@ -2611,13 +2689,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2662,22 +2740,22 @@
         <v>17672000</v>
       </c>
       <c r="S29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="X29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:24">
@@ -2685,13 +2763,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2736,22 +2814,22 @@
         <v>18128480</v>
       </c>
       <c r="S30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:24">
@@ -2759,13 +2837,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2810,22 +2888,22 @@
         <v>6762120</v>
       </c>
       <c r="S31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:24">
@@ -2833,13 +2911,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2884,22 +2962,22 @@
         <v>443709960</v>
       </c>
       <c r="S32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:24">
@@ -2907,13 +2985,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2958,22 +3036,22 @@
         <v>15320640</v>
       </c>
       <c r="S33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:24">
@@ -2981,13 +3059,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3032,22 +3110,22 @@
         <v>126035600</v>
       </c>
       <c r="S34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:24">
@@ -3055,13 +3133,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3106,22 +3184,22 @@
         <v>279582240</v>
       </c>
       <c r="S35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:24">
@@ -3129,13 +3207,13 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3180,22 +3258,22 @@
         <v>279582240</v>
       </c>
       <c r="S36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:24">
@@ -3203,13 +3281,13 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3254,22 +3332,22 @@
         <v>126035600</v>
       </c>
       <c r="S37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:24">
@@ -3277,13 +3355,13 @@
         <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -3328,22 +3406,22 @@
         <v>279582240</v>
       </c>
       <c r="S38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:24">
@@ -3351,13 +3429,13 @@
         <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3402,22 +3480,22 @@
         <v>126035600</v>
       </c>
       <c r="S39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:24">
@@ -3425,13 +3503,13 @@
         <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3476,22 +3554,22 @@
         <v>279582240</v>
       </c>
       <c r="S40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:24">
@@ -3499,13 +3577,13 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3550,22 +3628,22 @@
         <v>279582240</v>
       </c>
       <c r="S41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V41" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:24">
@@ -3573,13 +3651,13 @@
         <v>33</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3624,22 +3702,22 @@
         <v>279582240</v>
       </c>
       <c r="S42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V42" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:24">
@@ -3647,13 +3725,13 @@
         <v>33</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3698,22 +3776,22 @@
         <v>279582240</v>
       </c>
       <c r="S43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V43" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W43" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X43" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:24">
@@ -3721,13 +3799,13 @@
         <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3772,22 +3850,22 @@
         <v>279582240</v>
       </c>
       <c r="S44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T44" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V44" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X44" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:24">
@@ -3795,13 +3873,13 @@
         <v>34</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3846,22 +3924,22 @@
         <v>126035600</v>
       </c>
       <c r="S45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V45" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W45" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:24">
@@ -3869,13 +3947,13 @@
         <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3920,22 +3998,22 @@
         <v>279582240</v>
       </c>
       <c r="S46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U46" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X46" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:24">
@@ -3943,13 +4021,13 @@
         <v>35</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D47" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3994,22 +4072,22 @@
         <v>38744840</v>
       </c>
       <c r="S47" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T47" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V47" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W47" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X47" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:24">
@@ -4017,13 +4095,13 @@
         <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -4068,22 +4146,22 @@
         <v>38744840</v>
       </c>
       <c r="S48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T48" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V48" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:24">
@@ -4091,13 +4169,13 @@
         <v>35</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -4142,22 +4220,22 @@
         <v>38744840</v>
       </c>
       <c r="S49" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V49" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X49" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:24">
@@ -4165,13 +4243,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4216,22 +4294,22 @@
         <v>126035600</v>
       </c>
       <c r="S50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:24">
@@ -4239,13 +4317,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4290,22 +4368,22 @@
         <v>126035600</v>
       </c>
       <c r="S51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U51" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V51" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X51" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:24">
@@ -4313,13 +4391,13 @@
         <v>36</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -4364,22 +4442,22 @@
         <v>1928103120</v>
       </c>
       <c r="S52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U52" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V52" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X52" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:24">
@@ -4387,13 +4465,13 @@
         <v>37</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -4438,22 +4516,22 @@
         <v>200569200</v>
       </c>
       <c r="S53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U53" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W53" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X53" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:24">
@@ -4461,13 +4539,13 @@
         <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -4512,22 +4590,22 @@
         <v>126035600</v>
       </c>
       <c r="S54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U54" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V54" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X54" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:24">
@@ -4535,13 +4613,13 @@
         <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -4586,22 +4664,22 @@
         <v>279582240</v>
       </c>
       <c r="S55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U55" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W55" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X55" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:24">
@@ -4609,13 +4687,13 @@
         <v>32</v>
       </c>
       <c r="B56" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4660,22 +4738,22 @@
         <v>126035600</v>
       </c>
       <c r="S56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U56" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V56" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W56" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X56" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:24">
@@ -4683,13 +4761,13 @@
         <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4734,22 +4812,22 @@
         <v>1928103120</v>
       </c>
       <c r="S57" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T57" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U57" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V57" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W57" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X57" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:24">
@@ -4757,13 +4835,13 @@
         <v>32</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C58" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D58" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4808,22 +4886,22 @@
         <v>126035600</v>
       </c>
       <c r="S58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U58" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V58" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W58" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X58" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:24">
@@ -4831,13 +4909,13 @@
         <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D59" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -4882,22 +4960,22 @@
         <v>126035600</v>
       </c>
       <c r="S59" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T59" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U59" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V59" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W59" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:24">
@@ -4905,13 +4983,13 @@
         <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C60" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4956,22 +5034,22 @@
         <v>126035600</v>
       </c>
       <c r="S60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U60" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V60" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W60" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X60" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:24">
@@ -4979,13 +5057,13 @@
         <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C61" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D61" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -5030,22 +5108,22 @@
         <v>279582240</v>
       </c>
       <c r="S61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V61" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W61" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X61" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:24">
@@ -5053,13 +5131,13 @@
         <v>35</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C62" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D62" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -5104,22 +5182,22 @@
         <v>38744840</v>
       </c>
       <c r="S62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T62" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U62" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V62" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X62" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:24">
@@ -5127,13 +5205,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C63" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D63" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -5178,22 +5256,22 @@
         <v>443709960</v>
       </c>
       <c r="S63" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T63" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V63" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W63" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X63" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:24">
@@ -5201,13 +5279,13 @@
         <v>35</v>
       </c>
       <c r="B64" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D64" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -5252,22 +5330,22 @@
         <v>38744840</v>
       </c>
       <c r="S64" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T64" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U64" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V64" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X64" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:24">
@@ -5275,13 +5353,13 @@
         <v>32</v>
       </c>
       <c r="B65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C65" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D65" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -5326,22 +5404,22 @@
         <v>126035600</v>
       </c>
       <c r="S65" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T65" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W65" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X65" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:24">
@@ -5349,13 +5427,13 @@
         <v>32</v>
       </c>
       <c r="B66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C66" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D66" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -5400,22 +5478,22 @@
         <v>126035600</v>
       </c>
       <c r="S66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V66" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W66" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X66" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:24">
@@ -5423,13 +5501,13 @@
         <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C67" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D67" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -5474,22 +5552,22 @@
         <v>279582240</v>
       </c>
       <c r="S67" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T67" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U67" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V67" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W67" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X67" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:24">
@@ -5497,13 +5575,13 @@
         <v>32</v>
       </c>
       <c r="B68" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C68" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D68" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5548,22 +5626,22 @@
         <v>126035600</v>
       </c>
       <c r="S68" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T68" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U68" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V68" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W68" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X68" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:24">
@@ -5571,13 +5649,13 @@
         <v>39</v>
       </c>
       <c r="B69" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D69" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -5622,22 +5700,22 @@
         <v>2532703160</v>
       </c>
       <c r="S69" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T69" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U69" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V69" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W69" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X69" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:24">
@@ -5645,13 +5723,13 @@
         <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C70" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D70" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -5696,22 +5774,22 @@
         <v>279582240</v>
       </c>
       <c r="S70" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T70" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U70" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V70" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W70" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X70" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:24">
@@ -5719,13 +5797,13 @@
         <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C71" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D71" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -5770,22 +5848,22 @@
         <v>126035600</v>
       </c>
       <c r="S71" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T71" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U71" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V71" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W71" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X71" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="1:24">
@@ -5793,13 +5871,13 @@
         <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C72" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D72" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -5844,22 +5922,22 @@
         <v>126035600</v>
       </c>
       <c r="S72" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T72" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U72" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V72" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W72" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X72" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73" spans="1:24">
@@ -5867,13 +5945,13 @@
         <v>32</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C73" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D73" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5918,22 +5996,22 @@
         <v>126035600</v>
       </c>
       <c r="S73" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T73" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U73" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V73" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W73" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X73" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:24">
@@ -5941,13 +6019,13 @@
         <v>35</v>
       </c>
       <c r="B74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C74" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D74" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5992,22 +6070,22 @@
         <v>38744840</v>
       </c>
       <c r="S74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T74" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U74" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V74" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W74" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X74" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:24">
@@ -6015,13 +6093,13 @@
         <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C75" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D75" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -6066,22 +6144,22 @@
         <v>126035600</v>
       </c>
       <c r="S75" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T75" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U75" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V75" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W75" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X75" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="1:24">
@@ -6089,13 +6167,13 @@
         <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C76" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D76" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -6140,22 +6218,22 @@
         <v>279582240</v>
       </c>
       <c r="S76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T76" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U76" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V76" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W76" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X76" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:24">
@@ -6163,13 +6241,13 @@
         <v>35</v>
       </c>
       <c r="B77" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C77" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D77" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -6214,22 +6292,22 @@
         <v>38744840</v>
       </c>
       <c r="S77" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T77" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U77" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V77" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W77" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X77" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:24">
@@ -6237,13 +6315,13 @@
         <v>35</v>
       </c>
       <c r="B78" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C78" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D78" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -6288,22 +6366,22 @@
         <v>38744840</v>
       </c>
       <c r="S78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T78" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U78" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V78" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W78" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X78" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:24">
@@ -6311,13 +6389,13 @@
         <v>32</v>
       </c>
       <c r="B79" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C79" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D79" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -6362,22 +6440,22 @@
         <v>126035600</v>
       </c>
       <c r="S79" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T79" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U79" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V79" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W79" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X79" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" spans="1:24">
@@ -6385,13 +6463,13 @@
         <v>32</v>
       </c>
       <c r="B80" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C80" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D80" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -6436,22 +6514,22 @@
         <v>126035600</v>
       </c>
       <c r="S80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T80" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U80" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V80" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W80" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X80" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81" spans="1:24">
@@ -6459,13 +6537,13 @@
         <v>32</v>
       </c>
       <c r="B81" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C81" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D81" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -6510,22 +6588,22 @@
         <v>126035600</v>
       </c>
       <c r="S81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T81" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U81" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V81" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X81" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" spans="1:24">
@@ -6533,13 +6611,13 @@
         <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C82" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D82" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -6584,22 +6662,22 @@
         <v>126035600</v>
       </c>
       <c r="S82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T82" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U82" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V82" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X82" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:24">
@@ -6607,13 +6685,13 @@
         <v>32</v>
       </c>
       <c r="B83" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C83" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D83" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -6658,22 +6736,22 @@
         <v>126035600</v>
       </c>
       <c r="S83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T83" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U83" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V83" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W83" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X83" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:24">
@@ -6681,13 +6759,13 @@
         <v>32</v>
       </c>
       <c r="B84" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C84" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D84" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -6732,22 +6810,22 @@
         <v>126035600</v>
       </c>
       <c r="S84" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T84" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U84" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V84" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W84" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="X84" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:24">
@@ -6755,13 +6833,13 @@
         <v>32</v>
       </c>
       <c r="B85" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C85" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D85" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -6806,22 +6884,22 @@
         <v>126035600</v>
       </c>
       <c r="S85" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T85" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U85" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V85" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W85" t="s">
         <v>84</v>
       </c>
       <c r="X85" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:24">
@@ -6829,13 +6907,13 @@
         <v>32</v>
       </c>
       <c r="B86" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C86" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D86" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -6880,36 +6958,36 @@
         <v>126035600</v>
       </c>
       <c r="S86" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T86" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U86" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V86" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W86" t="s">
         <v>85</v>
       </c>
       <c r="X86" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" spans="1:24">
       <c r="A87" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B87" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C87" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D87" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -6918,13 +6996,13 @@
         <v>0</v>
       </c>
       <c r="G87">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="H87">
-        <v>501.3425414364641</v>
+        <v>2954.163265306122</v>
       </c>
       <c r="I87">
-        <v>6335088.651933702</v>
+        <v>213147.2040816327</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -6933,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="L87">
-        <v>61.41</v>
+        <v>39.52</v>
       </c>
       <c r="M87">
         <v>1</v>
@@ -6942,34 +7020,34 @@
         <v>0</v>
       </c>
       <c r="O87">
-        <v>44.56</v>
+        <v>35.81</v>
       </c>
       <c r="P87">
-        <v>15962276</v>
+        <v>487380</v>
       </c>
       <c r="Q87">
-        <v>1263</v>
+        <v>6755</v>
       </c>
       <c r="R87">
-        <v>1928103120</v>
+        <v>126035600</v>
       </c>
       <c r="S87" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T87" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="U87" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V87" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W87" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="X87" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:24">
@@ -6977,13 +7055,13 @@
         <v>36</v>
       </c>
       <c r="B88" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C88" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D88" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -7028,36 +7106,36 @@
         <v>1928103120</v>
       </c>
       <c r="S88" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T88" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U88" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V88" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W88" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="X88" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:24">
       <c r="A89" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B89" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C89" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D89" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -7066,13 +7144,13 @@
         <v>0</v>
       </c>
       <c r="G89">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="H89">
-        <v>2954.163265306122</v>
+        <v>501.3425414364641</v>
       </c>
       <c r="I89">
-        <v>213147.2040816327</v>
+        <v>6335088.651933702</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -7081,7 +7159,7 @@
         <v>0</v>
       </c>
       <c r="L89">
-        <v>39.52</v>
+        <v>61.41</v>
       </c>
       <c r="M89">
         <v>1</v>
@@ -7090,34 +7168,34 @@
         <v>0</v>
       </c>
       <c r="O89">
-        <v>35.81</v>
+        <v>44.56</v>
       </c>
       <c r="P89">
-        <v>487380</v>
+        <v>15962276</v>
       </c>
       <c r="Q89">
-        <v>6755</v>
+        <v>1263</v>
       </c>
       <c r="R89">
-        <v>126035600</v>
+        <v>1928103120</v>
       </c>
       <c r="S89" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T89" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="U89" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V89" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W89" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="X89" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:24">
@@ -7125,13 +7203,13 @@
         <v>39</v>
       </c>
       <c r="B90" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C90" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D90" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -7176,22 +7254,22 @@
         <v>2532703160</v>
       </c>
       <c r="S90" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T90" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U90" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V90" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W90" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X90" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" spans="1:24">
@@ -7199,13 +7277,13 @@
         <v>40</v>
       </c>
       <c r="B91" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C91" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D91" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -7250,22 +7328,22 @@
         <v>4332920</v>
       </c>
       <c r="S91" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T91" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U91" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W91" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X91" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92" spans="1:24">
@@ -7273,13 +7351,13 @@
         <v>32</v>
       </c>
       <c r="B92" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C92" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D92" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -7324,22 +7402,22 @@
         <v>126035600</v>
       </c>
       <c r="S92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U92" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V92" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W92" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" spans="1:24">
@@ -7347,13 +7425,13 @@
         <v>39</v>
       </c>
       <c r="B93" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C93" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D93" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -7398,22 +7476,22 @@
         <v>2532703160</v>
       </c>
       <c r="S93" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T93" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U93" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V93" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W93" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X93" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="94" spans="1:24">
@@ -7421,13 +7499,13 @@
         <v>35</v>
       </c>
       <c r="B94" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D94" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -7472,22 +7550,22 @@
         <v>38744840</v>
       </c>
       <c r="S94" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U94" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W94" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X94" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95" spans="1:24">
@@ -7495,13 +7573,13 @@
         <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C95" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D95" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -7546,22 +7624,22 @@
         <v>279582240</v>
       </c>
       <c r="S95" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T95" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U95" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V95" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W95" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X95" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="1:24">
@@ -7569,13 +7647,13 @@
         <v>35</v>
       </c>
       <c r="B96" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C96" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D96" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -7620,22 +7698,22 @@
         <v>38744840</v>
       </c>
       <c r="S96" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T96" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U96" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V96" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W96" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X96" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="97" spans="1:24">
@@ -7643,13 +7721,13 @@
         <v>35</v>
       </c>
       <c r="B97" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C97" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D97" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -7694,22 +7772,22 @@
         <v>38744840</v>
       </c>
       <c r="S97" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T97" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U97" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V97" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W97" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X97" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="98" spans="1:24">
@@ -7717,13 +7795,13 @@
         <v>35</v>
       </c>
       <c r="B98" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C98" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D98" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -7768,22 +7846,22 @@
         <v>38744840</v>
       </c>
       <c r="S98" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T98" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U98" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V98" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W98" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X98" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="99" spans="1:24">
@@ -7791,13 +7869,13 @@
         <v>35</v>
       </c>
       <c r="B99" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C99" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D99" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -7842,22 +7920,22 @@
         <v>38744840</v>
       </c>
       <c r="S99" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T99" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U99" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V99" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W99" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X99" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="100" spans="1:24">
@@ -7865,13 +7943,13 @@
         <v>32</v>
       </c>
       <c r="B100" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C100" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D100" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -7916,22 +7994,22 @@
         <v>126035600</v>
       </c>
       <c r="S100" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T100" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U100" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V100" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W100" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X100" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="101" spans="1:24">
@@ -7939,13 +8017,13 @@
         <v>32</v>
       </c>
       <c r="B101" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C101" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D101" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -7990,22 +8068,22 @@
         <v>126035600</v>
       </c>
       <c r="S101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T101" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U101" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V101" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W101" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X101" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="102" spans="1:24">
@@ -8013,13 +8091,13 @@
         <v>33</v>
       </c>
       <c r="B102" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C102" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D102" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -8064,22 +8142,22 @@
         <v>279582240</v>
       </c>
       <c r="S102" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T102" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U102" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V102" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W102" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X102" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="103" spans="1:24">
@@ -8087,13 +8165,13 @@
         <v>36</v>
       </c>
       <c r="B103" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C103" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D103" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -8138,22 +8216,22 @@
         <v>1928103120</v>
       </c>
       <c r="S103" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T103" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U103" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V103" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W103" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X103" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="104" spans="1:24">
@@ -8161,13 +8239,13 @@
         <v>39</v>
       </c>
       <c r="B104" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C104" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D104" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -8212,22 +8290,22 @@
         <v>2532703160</v>
       </c>
       <c r="S104" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T104" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U104" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V104" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W104" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X104" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="105" spans="1:24">
@@ -8235,13 +8313,13 @@
         <v>32</v>
       </c>
       <c r="B105" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C105" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D105" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -8286,22 +8364,22 @@
         <v>126035600</v>
       </c>
       <c r="S105" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T105" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U105" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V105" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W105" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X105" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="106" spans="1:24">
@@ -8309,13 +8387,13 @@
         <v>39</v>
       </c>
       <c r="B106" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C106" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D106" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -8360,36 +8438,36 @@
         <v>2532703160</v>
       </c>
       <c r="S106" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T106" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U106" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V106" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W106" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X106" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="107" spans="1:24">
       <c r="A107" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B107" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C107" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D107" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -8398,13 +8476,13 @@
         <v>0</v>
       </c>
       <c r="G107">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="H107">
-        <v>2954.163265306122</v>
+        <v>513.8311111111111</v>
       </c>
       <c r="I107">
-        <v>213147.2040816327</v>
+        <v>7871884.715555555</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -8413,7 +8491,7 @@
         <v>0</v>
       </c>
       <c r="L107">
-        <v>39.52</v>
+        <v>75.22</v>
       </c>
       <c r="M107">
         <v>1</v>
@@ -8422,34 +8500,34 @@
         <v>0</v>
       </c>
       <c r="O107">
-        <v>35.81</v>
+        <v>50.09</v>
       </c>
       <c r="P107">
-        <v>487380</v>
+        <v>20991693</v>
       </c>
       <c r="Q107">
-        <v>6755</v>
+        <v>1370</v>
       </c>
       <c r="R107">
-        <v>126035600</v>
+        <v>2532703160</v>
       </c>
       <c r="S107" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T107" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="U107" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V107" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W107" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="X107" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="108" spans="1:24">
@@ -8457,13 +8535,13 @@
         <v>32</v>
       </c>
       <c r="B108" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C108" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D108" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -8508,22 +8586,22 @@
         <v>126035600</v>
       </c>
       <c r="S108" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T108" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U108" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V108" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W108" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X108" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="109" spans="1:24">
@@ -8531,13 +8609,13 @@
         <v>32</v>
       </c>
       <c r="B109" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C109" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D109" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -8582,36 +8660,36 @@
         <v>126035600</v>
       </c>
       <c r="S109" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T109" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U109" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V109" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W109" t="s">
         <v>83</v>
       </c>
       <c r="X109" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="110" spans="1:24">
       <c r="A110" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B110" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C110" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D110" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -8620,13 +8698,13 @@
         <v>0</v>
       </c>
       <c r="G110">
-        <v>225</v>
+        <v>49</v>
       </c>
       <c r="H110">
-        <v>513.8311111111111</v>
+        <v>2954.163265306122</v>
       </c>
       <c r="I110">
-        <v>7871884.715555555</v>
+        <v>213147.2040816327</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -8635,7 +8713,7 @@
         <v>0</v>
       </c>
       <c r="L110">
-        <v>75.22</v>
+        <v>39.52</v>
       </c>
       <c r="M110">
         <v>1</v>
@@ -8644,48 +8722,48 @@
         <v>0</v>
       </c>
       <c r="O110">
-        <v>50.09</v>
+        <v>35.81</v>
       </c>
       <c r="P110">
-        <v>20991693</v>
+        <v>487380</v>
       </c>
       <c r="Q110">
-        <v>1370</v>
+        <v>6755</v>
       </c>
       <c r="R110">
-        <v>2532703160</v>
+        <v>126035600</v>
       </c>
       <c r="S110" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T110" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="U110" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V110" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W110" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X110" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="111" spans="1:24">
       <c r="A111" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B111" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C111" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D111" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -8694,13 +8772,13 @@
         <v>0</v>
       </c>
       <c r="G111">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="H111">
-        <v>2954.163265306122</v>
+        <v>513.8311111111111</v>
       </c>
       <c r="I111">
-        <v>213147.2040816327</v>
+        <v>7871884.715555555</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -8709,7 +8787,7 @@
         <v>0</v>
       </c>
       <c r="L111">
-        <v>39.52</v>
+        <v>75.22</v>
       </c>
       <c r="M111">
         <v>1</v>
@@ -8718,34 +8796,34 @@
         <v>0</v>
       </c>
       <c r="O111">
-        <v>35.81</v>
+        <v>50.09</v>
       </c>
       <c r="P111">
-        <v>487380</v>
+        <v>20991693</v>
       </c>
       <c r="Q111">
-        <v>6755</v>
+        <v>1370</v>
       </c>
       <c r="R111">
-        <v>126035600</v>
+        <v>2532703160</v>
       </c>
       <c r="S111" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T111" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="U111" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V111" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W111" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="X111" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="112" spans="1:24">
@@ -8753,13 +8831,13 @@
         <v>32</v>
       </c>
       <c r="B112" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C112" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D112" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -8804,36 +8882,36 @@
         <v>126035600</v>
       </c>
       <c r="S112" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T112" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U112" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V112" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W112" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="X112" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="113" spans="1:24">
       <c r="A113" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B113" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C113" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D113" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -8842,13 +8920,13 @@
         <v>0</v>
       </c>
       <c r="G113">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H113">
-        <v>11.92592592592593</v>
+        <v>2954.163265306122</v>
       </c>
       <c r="I113">
-        <v>166739.2962962963</v>
+        <v>213147.2040816327</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -8857,7 +8935,7 @@
         <v>0</v>
       </c>
       <c r="L113">
-        <v>5.56</v>
+        <v>39.52</v>
       </c>
       <c r="M113">
         <v>1</v>
@@ -8866,48 +8944,48 @@
         <v>0</v>
       </c>
       <c r="O113">
-        <v>22.22</v>
+        <v>35.81</v>
       </c>
       <c r="P113">
-        <v>320957</v>
+        <v>487380</v>
       </c>
       <c r="Q113">
-        <v>23</v>
+        <v>6755</v>
       </c>
       <c r="R113">
-        <v>38744840</v>
+        <v>126035600</v>
       </c>
       <c r="S113" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T113" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U113" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V113" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W113" t="s">
         <v>83</v>
       </c>
       <c r="X113" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="114" spans="1:24">
       <c r="A114" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B114" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D114" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -8916,13 +8994,13 @@
         <v>0</v>
       </c>
       <c r="G114">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H114">
-        <v>2954.163265306122</v>
+        <v>11.92592592592593</v>
       </c>
       <c r="I114">
-        <v>213147.2040816327</v>
+        <v>166739.2962962963</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -8931,7 +9009,7 @@
         <v>0</v>
       </c>
       <c r="L114">
-        <v>39.52</v>
+        <v>5.56</v>
       </c>
       <c r="M114">
         <v>1</v>
@@ -8940,48 +9018,48 @@
         <v>0</v>
       </c>
       <c r="O114">
-        <v>35.81</v>
+        <v>22.22</v>
       </c>
       <c r="P114">
-        <v>487380</v>
+        <v>320957</v>
       </c>
       <c r="Q114">
-        <v>6755</v>
+        <v>23</v>
       </c>
       <c r="R114">
-        <v>126035600</v>
+        <v>38744840</v>
       </c>
       <c r="S114" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T114" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U114" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V114" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W114" t="s">
         <v>84</v>
       </c>
       <c r="X114" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="115" spans="1:24">
       <c r="A115" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B115" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C115" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D115" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -8990,13 +9068,13 @@
         <v>0</v>
       </c>
       <c r="G115">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="H115">
-        <v>501.3425414364641</v>
+        <v>2954.163265306122</v>
       </c>
       <c r="I115">
-        <v>6335088.651933702</v>
+        <v>213147.2040816327</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -9005,7 +9083,7 @@
         <v>0</v>
       </c>
       <c r="L115">
-        <v>61.41</v>
+        <v>39.52</v>
       </c>
       <c r="M115">
         <v>1</v>
@@ -9014,48 +9092,48 @@
         <v>0</v>
       </c>
       <c r="O115">
-        <v>44.56</v>
+        <v>35.81</v>
       </c>
       <c r="P115">
-        <v>15962276</v>
+        <v>487380</v>
       </c>
       <c r="Q115">
-        <v>1263</v>
+        <v>6755</v>
       </c>
       <c r="R115">
-        <v>1928103120</v>
+        <v>126035600</v>
       </c>
       <c r="S115" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T115" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="U115" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V115" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W115" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="X115" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="116" spans="1:24">
       <c r="A116" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B116" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C116" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -9064,13 +9142,13 @@
         <v>0</v>
       </c>
       <c r="G116">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="H116">
-        <v>2954.163265306122</v>
+        <v>501.3425414364641</v>
       </c>
       <c r="I116">
-        <v>213147.2040816327</v>
+        <v>6335088.651933702</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -9079,7 +9157,7 @@
         <v>0</v>
       </c>
       <c r="L116">
-        <v>39.52</v>
+        <v>61.41</v>
       </c>
       <c r="M116">
         <v>1</v>
@@ -9088,48 +9166,48 @@
         <v>0</v>
       </c>
       <c r="O116">
-        <v>35.81</v>
+        <v>44.56</v>
       </c>
       <c r="P116">
-        <v>487380</v>
+        <v>15962276</v>
       </c>
       <c r="Q116">
-        <v>6755</v>
+        <v>1263</v>
       </c>
       <c r="R116">
-        <v>126035600</v>
+        <v>1928103120</v>
       </c>
       <c r="S116" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T116" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="U116" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V116" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W116" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="X116" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="117" spans="1:24">
       <c r="A117" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B117" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C117" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D117" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -9138,13 +9216,13 @@
         <v>0</v>
       </c>
       <c r="G117">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H117">
-        <v>11.92592592592593</v>
+        <v>2954.163265306122</v>
       </c>
       <c r="I117">
-        <v>166739.2962962963</v>
+        <v>213147.2040816327</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -9153,7 +9231,7 @@
         <v>0</v>
       </c>
       <c r="L117">
-        <v>5.56</v>
+        <v>39.52</v>
       </c>
       <c r="M117">
         <v>1</v>
@@ -9162,34 +9240,34 @@
         <v>0</v>
       </c>
       <c r="O117">
-        <v>22.22</v>
+        <v>35.81</v>
       </c>
       <c r="P117">
-        <v>320957</v>
+        <v>487380</v>
       </c>
       <c r="Q117">
-        <v>23</v>
+        <v>6755</v>
       </c>
       <c r="R117">
-        <v>38744840</v>
+        <v>126035600</v>
       </c>
       <c r="S117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U117" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V117" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W117" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="X117" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="118" spans="1:24">
@@ -9197,13 +9275,13 @@
         <v>35</v>
       </c>
       <c r="B118" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C118" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D118" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -9248,36 +9326,36 @@
         <v>38744840</v>
       </c>
       <c r="S118" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T118" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U118" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V118" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W118" t="s">
         <v>76</v>
       </c>
       <c r="X118" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="119" spans="1:24">
       <c r="A119" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B119" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C119" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D119" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -9286,13 +9364,13 @@
         <v>0</v>
       </c>
       <c r="G119">
-        <v>225</v>
+        <v>27</v>
       </c>
       <c r="H119">
-        <v>513.8311111111111</v>
+        <v>11.92592592592593</v>
       </c>
       <c r="I119">
-        <v>7871884.715555555</v>
+        <v>166739.2962962963</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -9301,7 +9379,7 @@
         <v>0</v>
       </c>
       <c r="L119">
-        <v>75.22</v>
+        <v>5.56</v>
       </c>
       <c r="M119">
         <v>1</v>
@@ -9310,48 +9388,48 @@
         <v>0</v>
       </c>
       <c r="O119">
-        <v>50.09</v>
+        <v>22.22</v>
       </c>
       <c r="P119">
-        <v>20991693</v>
+        <v>320957</v>
       </c>
       <c r="Q119">
-        <v>1370</v>
+        <v>23</v>
       </c>
       <c r="R119">
-        <v>2532703160</v>
+        <v>38744840</v>
       </c>
       <c r="S119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T119" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="U119" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V119" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W119" t="s">
         <v>77</v>
       </c>
       <c r="X119" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="120" spans="1:24">
       <c r="A120" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B120" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C120" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D120" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -9360,13 +9438,13 @@
         <v>0</v>
       </c>
       <c r="G120">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="H120">
-        <v>2954.163265306122</v>
+        <v>513.8311111111111</v>
       </c>
       <c r="I120">
-        <v>213147.2040816327</v>
+        <v>7871884.715555555</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -9375,7 +9453,7 @@
         <v>0</v>
       </c>
       <c r="L120">
-        <v>39.52</v>
+        <v>75.22</v>
       </c>
       <c r="M120">
         <v>1</v>
@@ -9384,48 +9462,48 @@
         <v>0</v>
       </c>
       <c r="O120">
-        <v>35.81</v>
+        <v>50.09</v>
       </c>
       <c r="P120">
-        <v>487380</v>
+        <v>20991693</v>
       </c>
       <c r="Q120">
-        <v>6755</v>
+        <v>1370</v>
       </c>
       <c r="R120">
-        <v>126035600</v>
+        <v>2532703160</v>
       </c>
       <c r="S120" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T120" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="U120" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V120" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W120" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="X120" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="121" spans="1:24">
       <c r="A121" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B121" t="s">
         <v>49</v>
       </c>
       <c r="C121" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D121" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -9434,13 +9512,13 @@
         <v>0</v>
       </c>
       <c r="G121">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="H121">
-        <v>146.1139240506329</v>
+        <v>2954.163265306122</v>
       </c>
       <c r="I121">
-        <v>1110046.696202532</v>
+        <v>213147.2040816327</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -9449,7 +9527,7 @@
         <v>0</v>
       </c>
       <c r="L121">
-        <v>19.76</v>
+        <v>39.52</v>
       </c>
       <c r="M121">
         <v>1</v>
@@ -9458,48 +9536,48 @@
         <v>0</v>
       </c>
       <c r="O121">
-        <v>27.9</v>
+        <v>35.81</v>
       </c>
       <c r="P121">
-        <v>2304602</v>
+        <v>487380</v>
       </c>
       <c r="Q121">
-        <v>303</v>
+        <v>6755</v>
       </c>
       <c r="R121">
-        <v>279582240</v>
+        <v>126035600</v>
       </c>
       <c r="S121" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T121" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U121" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V121" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W121" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="X121" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122" spans="1:24">
       <c r="A122" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B122" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C122" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D122" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -9508,13 +9586,13 @@
         <v>0</v>
       </c>
       <c r="G122">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H122">
-        <v>2954.163265306122</v>
+        <v>146.1139240506329</v>
       </c>
       <c r="I122">
-        <v>213147.2040816327</v>
+        <v>1110046.696202532</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -9523,7 +9601,7 @@
         <v>0</v>
       </c>
       <c r="L122">
-        <v>39.52</v>
+        <v>19.76</v>
       </c>
       <c r="M122">
         <v>1</v>
@@ -9532,34 +9610,34 @@
         <v>0</v>
       </c>
       <c r="O122">
-        <v>35.81</v>
+        <v>27.9</v>
       </c>
       <c r="P122">
-        <v>487380</v>
+        <v>2304602</v>
       </c>
       <c r="Q122">
-        <v>6755</v>
+        <v>303</v>
       </c>
       <c r="R122">
-        <v>126035600</v>
+        <v>279582240</v>
       </c>
       <c r="S122" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T122" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U122" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V122" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W122" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X122" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="123" spans="1:24">
@@ -9567,13 +9645,13 @@
         <v>32</v>
       </c>
       <c r="B123" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C123" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D123" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -9618,36 +9696,36 @@
         <v>126035600</v>
       </c>
       <c r="S123" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T123" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U123" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V123" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W123" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X123" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="124" spans="1:24">
       <c r="A124" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B124" t="s">
         <v>49</v>
       </c>
       <c r="C124" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D124" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -9656,13 +9734,13 @@
         <v>0</v>
       </c>
       <c r="G124">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="H124">
-        <v>146.1139240506329</v>
+        <v>2954.163265306122</v>
       </c>
       <c r="I124">
-        <v>1110046.696202532</v>
+        <v>213147.2040816327</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -9671,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="L124">
-        <v>19.76</v>
+        <v>39.52</v>
       </c>
       <c r="M124">
         <v>1</v>
@@ -9680,48 +9758,48 @@
         <v>0</v>
       </c>
       <c r="O124">
-        <v>27.9</v>
+        <v>35.81</v>
       </c>
       <c r="P124">
-        <v>2304602</v>
+        <v>487380</v>
       </c>
       <c r="Q124">
-        <v>303</v>
+        <v>6755</v>
       </c>
       <c r="R124">
-        <v>279582240</v>
+        <v>126035600</v>
       </c>
       <c r="S124" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T124" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U124" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V124" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W124" t="s">
         <v>77</v>
       </c>
       <c r="X124" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="125" spans="1:24">
       <c r="A125" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B125" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C125" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D125" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -9730,13 +9808,13 @@
         <v>0</v>
       </c>
       <c r="G125">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H125">
-        <v>2954.163265306122</v>
+        <v>146.1139240506329</v>
       </c>
       <c r="I125">
-        <v>213147.2040816327</v>
+        <v>1110046.696202532</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -9745,7 +9823,7 @@
         <v>0</v>
       </c>
       <c r="L125">
-        <v>39.52</v>
+        <v>19.76</v>
       </c>
       <c r="M125">
         <v>1</v>
@@ -9754,34 +9832,34 @@
         <v>0</v>
       </c>
       <c r="O125">
-        <v>35.81</v>
+        <v>27.9</v>
       </c>
       <c r="P125">
-        <v>487380</v>
+        <v>2304602</v>
       </c>
       <c r="Q125">
-        <v>6755</v>
+        <v>303</v>
       </c>
       <c r="R125">
-        <v>126035600</v>
+        <v>279582240</v>
       </c>
       <c r="S125" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T125" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U125" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V125" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W125" t="s">
         <v>78</v>
       </c>
       <c r="X125" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
